--- a/02_指示書検証テスト/01_PoC資料/02_指示書AI_PoCテスト結果一覧.xlsx
+++ b/02_指示書検証テスト/01_PoC資料/02_指示書AI_PoCテスト結果一覧.xlsx
@@ -1,21 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.0.240\gyomu-share\配車用\個人フォルダ\関東統括ｾﾝﾀｰ区域（三郷）\●個人配車日報保存場所\パートさん日報置き場\笹沼仁美\指示書検証テスト\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\chito\coachtech\dispatch-automation-project\02_指示書検証テスト\01_PoC資料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF5F013F-AC70-4B2F-AB9E-6904B226B945}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E27D566B-85AA-4192-9421-E017A2509DC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_テスト結果一覧" sheetId="1" r:id="rId1"/>
     <sheet name="02_T01-T10判定基準" sheetId="2" r:id="rId2"/>
     <sheet name="03_入力ルール" sheetId="3" r:id="rId3"/>
+    <sheet name="04_読込結果反映プロンプト" sheetId="4" r:id="rId4"/>
+    <sheet name="99_旧時間項目退避" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -26,6 +28,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -33,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="303">
   <si>
     <t>配車指示書AI PoC テスト結果一覧</t>
   </si>
@@ -143,12 +147,15 @@
     <t>D001</t>
   </si>
   <si>
-    <t>関東</t>
+    <t>T01</t>
   </si>
   <si>
     <t>D002</t>
   </si>
   <si>
+    <t>T05</t>
+  </si>
+  <si>
     <t>D003</t>
   </si>
   <si>
@@ -461,9 +468,6 @@
     <t>備考</t>
   </si>
   <si>
-    <t>T01</t>
-  </si>
-  <si>
     <t>一般的な印字帳票</t>
   </si>
   <si>
@@ -536,9 +540,6 @@
     <t>レイアウト非依存</t>
   </si>
   <si>
-    <t>T05</t>
-  </si>
-  <si>
     <t>複数積地・卸地</t>
   </si>
   <si>
@@ -734,34 +735,288 @@
     <t>安全項目は1件でもNGあり</t>
   </si>
   <si>
-    <t>九州</t>
-  </si>
-  <si>
-    <t>軽い</t>
-  </si>
-  <si>
-    <t>なし</t>
-  </si>
-  <si>
-    <t>可</t>
-  </si>
-  <si>
-    <t>積地卸地の建物名称がその他になっていた</t>
-  </si>
-  <si>
-    <t>合格</t>
+    <t>処理開始時刻</t>
+  </si>
+  <si>
+    <t>画像読込開始時刻</t>
+  </si>
+  <si>
+    <t>画像読込完了時刻</t>
+  </si>
+  <si>
+    <t>画像読込所要時間(秒)</t>
+  </si>
+  <si>
+    <t>処理完了時刻</t>
+  </si>
+  <si>
+    <t>Excel書込開始時刻</t>
+  </si>
+  <si>
+    <t>PDF出力完了時刻</t>
+  </si>
+  <si>
+    <t>Excel書込・PDF出力所要時間(秒)</t>
+  </si>
+  <si>
+    <t>記載なし項目数</t>
+  </si>
+  <si>
+    <t>矛盾項目数</t>
+  </si>
+  <si>
+    <t>AIが人に確認を戻した項目数</t>
+  </si>
+  <si>
+    <t>読込結果反映状況</t>
+  </si>
+  <si>
+    <t>読込結果反映メモ</t>
+  </si>
+  <si>
+    <t>依頼を受け、処理を開始する直前の時刻</t>
+  </si>
+  <si>
+    <t>2026/10/02 15:30:01</t>
+  </si>
+  <si>
+    <t>取得できない場合は推測せず『時刻取得不可』</t>
+  </si>
+  <si>
+    <t>画像読込開始／完了時刻</t>
+  </si>
+  <si>
+    <t>画像読込開始直前と、読込・抽出・要確認判定が完了した時刻</t>
+  </si>
+  <si>
+    <t>開始 15:30:03／完了 15:30:12</t>
+  </si>
+  <si>
+    <t>JSTで記録。内部時刻が取得不能なら推測しない</t>
+  </si>
+  <si>
+    <t>画像読込開始時刻から画像読込完了時刻までの差</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>秒単位。開始・完了のどちらかが取得不能なら空欄</t>
+  </si>
+  <si>
+    <t>01_指示書読込プロンプトの回答・判定まで含めた処理が完了する直前の時刻</t>
+  </si>
+  <si>
+    <t>2026/10/02 15:30:15</t>
+  </si>
+  <si>
+    <t>画像読込完了時刻やPDF出力完了時刻とは分けて記録</t>
+  </si>
+  <si>
+    <t>読込結果の『記載なしの情報』に分類された項目数</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>項目名だけ数え、内容をこの一覧へ転記しない</t>
+  </si>
+  <si>
+    <t>読込結果の『矛盾している情報』に分類された項目数</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>矛盾内容そのものは必要に応じ反映メモへ匿名で記載</t>
+  </si>
+  <si>
+    <t>AIが推測せず、人の確認へ戻した項目数</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>『要確認項目数』と意味が重なる場合も、読込出力の値をそのまま記録</t>
+  </si>
+  <si>
+    <t>読込結果をテスト結果一覧へ転記した状態</t>
+  </si>
+  <si>
+    <t>未反映／一部反映／反映済／要確認</t>
+  </si>
+  <si>
+    <t>手作業・AI反映どちらでも同じ区分を使用</t>
+  </si>
+  <si>
+    <t>人の判定が必要な項目</t>
+  </si>
+  <si>
+    <t>誤読、勝手に確定、順序誤り、禁止情報誤出力、合否など</t>
+  </si>
+  <si>
+    <t>読込結果のみでは空欄</t>
+  </si>
+  <si>
+    <t>AI自身の読込結果だけから0件・合格と決めない</t>
+  </si>
+  <si>
+    <t>読込結果をExcelテンプレートへ反映するため、最初のセルへの書き込み・変更を開始する直前の時刻</t>
+  </si>
+  <si>
+    <t>2026/10/02 15:31:00</t>
+  </si>
+  <si>
+    <t>テンプレート確認のみの時間は含めない。JSTで記録し、推測しない</t>
+  </si>
+  <si>
+    <t>Excelへの入力・確認・保存後、PDF生成が完了し、出力ファイルの存在を確認した時刻</t>
+  </si>
+  <si>
+    <t>2026/10/02 15:31:42</t>
+  </si>
+  <si>
+    <t>Excel保存時刻ではなくPDF生成完了時刻を使用</t>
+  </si>
+  <si>
+    <t>Excel書込開始時刻からPDF出力完了時刻までの差</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>開始・完了のどちらかが取得不能なら空欄。画像読込時間を代用しない</t>
+  </si>
+  <si>
+    <t>指示書読込・出力結果 → PoCテスト結果一覧 反映プロンプト</t>
+  </si>
+  <si>
+    <t>使い方</t>
+  </si>
+  <si>
+    <t>内容</t>
+  </si>
+  <si>
+    <t>このExcelと、01_指示書読込プロンプトの読込結果、02_指示書出力プロンプトの処理時間結果を同じ依頼に添付します。</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>対象のケースID（例：D003）を必ず指定します。</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>下の『コピー用プロンプト』をそのまま使用します。</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>AI判定だけで決められない項目は空欄のままにし、人の確認後に入力します。</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>会社名・住所・電話番号・FAX・運賃・商品実値など、原本の具体情報はテスト結果一覧へ転記しません。</t>
+  </si>
+  <si>
+    <t>コピー用プロンプト</t>
+  </si>
+  <si>
+    <t>【目的】
+添付された「01_指示書読込プロンプト」の読込結果と、
+「02_指示書出力プロンプト」のExcel書込・PDF出力時間を、
+「02_指示書AI_PoCテスト結果一覧.xlsx」の
+「01_テスト結果一覧」へ反映してください。
+【対象ケース】
+ケースID：DXXX
+※必ず指定されたケースIDとC列「ケースID」が一致する行だけを更新してください。
+※一致するケースIDがない場合は、新しい行を勝手に作成せず「対象ケースなし」と報告してください。
+【反映する項目】
+読込結果・出力結果から明確に取得できる場合のみ、以下を反映してください。
+・O列「明確に読取れた項目数」
+・P列「要確認項目数」
+・AA列「処理開始時刻」
+　← 01読込結果の「■処理開始時刻」
+・AB列「画像読込開始時刻」
+　← 01読込結果の「■画像読込開始時刻」
+・AC列「画像読込完了時刻」
+　← 01読込結果の「■画像読込完了時刻」
+・AD列「画像読込所要時間(秒)」
+　← 01読込結果の「■画像読込所要時間」の数値部分
+・AE列「処理完了時刻」
+　← 01読込結果の「■処理完了時刻」
+・AF列「Excel書込開始時刻」
+　← 02出力結果の「■Excel書込開始時刻」
+・AG列「PDF出力完了時刻」
+　← 02出力結果の「■PDF出力完了時刻」
+・AH列「Excel書込・PDF出力所要時間(秒)」
+　← 02出力結果の「■Excel書込・PDF出力所要時間」の総秒数
+・AI列「記載なし項目数」
+・AJ列「矛盾項目数」
+・AK列「AIが人に確認を戻した項目数」
+・AL列「読込結果反映状況」
+・AM列「読込結果反映メモ」
+【時間の重要ルール】
+- 「画像読込所要時間」と「Excel書込・PDF出力所要時間」は別区間として記録してください。
+- 片方の時間をもう片方へ代用しないでください。
+- 取得できない時刻・時間は推測せず空欄にしてください。
+- 旧項目「読み込み時間」「処理時間（読込→PDF完了）」は使用しません。
+【自動で入力してはいけない項目】
+Q列「誤読件数」
+R列「勝手に確定した件数」
+S列「積地・卸地順序誤り件数」
+T列「禁止情報誤出力件数」
+U列「テンプレート自動入力」
+V列「修正内容」
+W列「判定者」
+X列「配車担当確認」
+Y列「合否」
+これらは必要な資料・人の確認が揃った場合のみ入力してください。
+【情報の取り扱い】
+- 具体的な会社名、詳細住所、電話番号、FAX番号、運賃、商品内容等はテスト結果一覧へ転記しないでください。
+- 件数・時間・判定・匿名化した確認メモだけを記録してください。
+- 既存値と新しい値が異なる場合は勝手に上書きせず「要確認」としてください。
+【完了時の報告】
+更新したケースID：
+更新したセル：
+更新できなかった項目：
+人の確認が必要な項目：</t>
+  </si>
+  <si>
+    <t>旧行番号</t>
+  </si>
+  <si>
+    <t>旧：読み込み時間</t>
+  </si>
+  <si>
+    <t>旧：処理時間（読込→PDF完了）</t>
+  </si>
+  <si>
+    <t>2026/10/01 22:54:11</t>
+  </si>
+  <si>
+    <t>2分24秒</t>
+  </si>
+  <si>
+    <t>列構成変更前の旧時間項目。新しい2区間計測には自動変換していません。</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="176" formatCode="0.0%"/>
     <numFmt numFmtId="177" formatCode="0.0"/>
     <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="yyyy/mm/dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -816,8 +1071,18 @@
       <family val="3"/>
       <charset val="128"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF203B5B"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Carlito"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -827,6 +1092,21 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EAF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4472C4"/>
       </patternFill>
     </fill>
     <fill>
@@ -853,7 +1133,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -885,19 +1165,54 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -912,7 +1227,7 @@
         <color rgb="FF7F6000"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFFF2CC"/>
         </patternFill>
       </fill>
@@ -923,7 +1238,7 @@
         <color rgb="FF9C0006"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFCE4D6"/>
         </patternFill>
       </fill>
@@ -934,14 +1249,14 @@
         <color rgb="FF006100"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFE2F0D9"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFF4CCCC"/>
         </patternFill>
       </fill>
@@ -1154,8 +1469,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z120"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <dimension ref="A1:AM120"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -1180,39 +1495,58 @@
     <col min="24" max="24" width="14" customWidth="1"/>
     <col min="25" max="25" width="10" customWidth="1"/>
     <col min="26" max="26" width="32" customWidth="1"/>
+    <col min="27" max="29" width="20" customWidth="1"/>
+    <col min="30" max="30" width="18" customWidth="1"/>
+    <col min="31" max="33" width="20" customWidth="1"/>
+    <col min="34" max="34" width="22" customWidth="1"/>
+    <col min="35" max="37" width="18" customWidth="1"/>
+    <col min="38" max="38" width="16" customWidth="1"/>
+    <col min="39" max="39" width="32" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="26.1" customHeight="1">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:39" ht="17.399999999999999" customHeight="1">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
-      <c r="K1" s="12"/>
-      <c r="L1" s="12"/>
-      <c r="M1" s="12"/>
-      <c r="N1" s="12"/>
-      <c r="O1" s="12"/>
-      <c r="P1" s="12"/>
-      <c r="Q1" s="12"/>
-      <c r="R1" s="12"/>
-      <c r="S1" s="12"/>
-      <c r="T1" s="12"/>
-      <c r="U1" s="12"/>
-      <c r="V1" s="12"/>
-      <c r="W1" s="12"/>
-      <c r="X1" s="12"/>
-      <c r="Y1" s="12"/>
-      <c r="Z1" s="12"/>
-    </row>
-    <row r="2" spans="1:26">
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="23"/>
+      <c r="M1" s="23"/>
+      <c r="N1" s="23"/>
+      <c r="O1" s="23"/>
+      <c r="P1" s="23"/>
+      <c r="Q1" s="23"/>
+      <c r="R1" s="23"/>
+      <c r="S1" s="23"/>
+      <c r="T1" s="23"/>
+      <c r="U1" s="23"/>
+      <c r="V1" s="23"/>
+      <c r="W1" s="23"/>
+      <c r="X1" s="23"/>
+      <c r="Y1" s="23"/>
+      <c r="Z1" s="23"/>
+      <c r="AA1" s="24"/>
+      <c r="AB1" s="24"/>
+      <c r="AC1" s="24"/>
+      <c r="AD1" s="24"/>
+      <c r="AE1" s="24"/>
+      <c r="AF1" s="24"/>
+      <c r="AG1" s="24"/>
+      <c r="AH1" s="24"/>
+      <c r="AI1" s="24"/>
+      <c r="AJ1" s="24"/>
+      <c r="AK1" s="24"/>
+      <c r="AL1" s="24"/>
+    </row>
+    <row r="2" spans="1:39">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -1240,7 +1574,7 @@
       <c r="Y2" s="2"/>
       <c r="Z2" s="2"/>
     </row>
-    <row r="3" spans="1:26" ht="45">
+    <row r="3" spans="1:39" ht="28">
       <c r="A3" s="6" t="s">
         <v>1</v>
       </c>
@@ -1284,14 +1618,14 @@
       <c r="Y3" s="2"/>
       <c r="Z3" s="2"/>
     </row>
-    <row r="4" spans="1:26" ht="15.75">
+    <row r="4" spans="1:39" ht="15.5">
       <c r="A4" s="7">
         <f>COUNTA(C7:C106)</f>
         <v>100</v>
       </c>
       <c r="B4" s="7">
         <f>COUNTIF(Y7:Y106,"合格")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" s="7">
         <f>COUNTIF(Y7:Y106,"不合格")</f>
@@ -1299,7 +1633,7 @@
       </c>
       <c r="D4" s="8">
         <f>IF(A4=0,"",B4/A4)</f>
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="E4" s="7">
         <f>SUM(Q7:Q106)</f>
@@ -1313,9 +1647,9 @@
         <f>SUM(T7:T106)</f>
         <v>0</v>
       </c>
-      <c r="H4" s="9">
+      <c r="H4" s="9" t="str">
         <f>IFERROR(AVERAGE(N7:N106),"")</f>
-        <v>5</v>
+        <v/>
       </c>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
@@ -1336,7 +1670,7 @@
       <c r="Y4" s="2"/>
       <c r="Z4" s="2"/>
     </row>
-    <row r="5" spans="1:26">
+    <row r="5" spans="1:39">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1364,7 +1698,7 @@
       <c r="Y5" s="2"/>
       <c r="Z5" s="2"/>
     </row>
-    <row r="6" spans="1:26" ht="30">
+    <row r="6" spans="1:39" ht="28" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
@@ -1443,8 +1777,47 @@
       <c r="Z6" s="1" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="7" spans="1:26" ht="27">
+      <c r="AA6" s="15" t="s">
+        <v>232</v>
+      </c>
+      <c r="AB6" s="15" t="s">
+        <v>233</v>
+      </c>
+      <c r="AC6" s="15" t="s">
+        <v>234</v>
+      </c>
+      <c r="AD6" s="15" t="s">
+        <v>235</v>
+      </c>
+      <c r="AE6" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="AF6" s="15" t="s">
+        <v>237</v>
+      </c>
+      <c r="AG6" s="15" t="s">
+        <v>238</v>
+      </c>
+      <c r="AH6" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="AI6" s="15" t="s">
+        <v>240</v>
+      </c>
+      <c r="AJ6" s="15" t="s">
+        <v>241</v>
+      </c>
+      <c r="AK6" s="15" t="s">
+        <v>242</v>
+      </c>
+      <c r="AL6" s="15" t="s">
+        <v>243</v>
+      </c>
+      <c r="AM6" s="20" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="7" spans="1:39">
       <c r="A7" s="2">
         <v>1</v>
       </c>
@@ -1452,66 +1825,43 @@
       <c r="C7" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>142</v>
-      </c>
+      <c r="D7" s="2"/>
       <c r="E7" s="2"/>
-      <c r="F7" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="J7" s="4">
-        <v>21</v>
-      </c>
-      <c r="K7" s="4">
-        <v>5</v>
-      </c>
-      <c r="L7" s="4"/>
-      <c r="M7" s="4"/>
-      <c r="N7" s="4">
-        <f t="shared" ref="N7:N38" si="0">IF(COUNTA(K7:M7)=0,"",SUM(K7:M7))</f>
-        <v>5</v>
-      </c>
-      <c r="O7" s="4">
-        <v>21</v>
-      </c>
-      <c r="P7" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="4">
-        <v>0</v>
-      </c>
-      <c r="R7" s="4">
-        <v>0</v>
-      </c>
-      <c r="S7" s="4">
-        <v>0</v>
-      </c>
-      <c r="T7" s="4">
-        <v>0</v>
-      </c>
-      <c r="U7" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="V7" s="14"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="21"/>
+      <c r="L7" s="21"/>
+      <c r="M7" s="21"/>
+      <c r="N7" s="21"/>
+      <c r="O7" s="4"/>
+      <c r="P7" s="4"/>
+      <c r="Q7" s="4"/>
+      <c r="R7" s="4"/>
+      <c r="S7" s="4"/>
+      <c r="T7" s="4"/>
+      <c r="U7" s="2"/>
+      <c r="V7" s="11"/>
       <c r="W7" s="5"/>
       <c r="X7" s="5"/>
-      <c r="Y7" s="5" t="s">
-        <v>238</v>
-      </c>
-      <c r="Z7" s="15" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="8" spans="1:26">
+      <c r="Y7" s="5"/>
+      <c r="Z7" s="12"/>
+      <c r="AA7" s="13"/>
+      <c r="AB7" s="13"/>
+      <c r="AC7" s="16"/>
+      <c r="AD7" s="16"/>
+      <c r="AE7" s="16"/>
+      <c r="AF7" s="17"/>
+      <c r="AG7" s="16"/>
+      <c r="AH7" s="17"/>
+      <c r="AI7" s="17"/>
+      <c r="AJ7" s="17"/>
+      <c r="AK7" s="14"/>
+      <c r="AL7" s="14"/>
+    </row>
+    <row r="8" spans="1:39">
       <c r="A8" s="2">
         <v>2</v>
       </c>
@@ -1521,9 +1871,7 @@
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
-      <c r="F8" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F8" s="2"/>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
@@ -1531,10 +1879,7 @@
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
       <c r="M8" s="4"/>
-      <c r="N8" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="N8" s="4"/>
       <c r="O8" s="4"/>
       <c r="P8" s="4"/>
       <c r="Q8" s="4"/>
@@ -1546,21 +1891,31 @@
       <c r="W8" s="5"/>
       <c r="X8" s="5"/>
       <c r="Y8" s="5"/>
-      <c r="Z8" s="5"/>
-    </row>
-    <row r="9" spans="1:26">
+      <c r="Z8" s="12"/>
+      <c r="AA8" s="13"/>
+      <c r="AB8" s="13"/>
+      <c r="AC8" s="16"/>
+      <c r="AD8" s="16"/>
+      <c r="AE8" s="16"/>
+      <c r="AF8" s="17"/>
+      <c r="AG8" s="16"/>
+      <c r="AH8" s="17"/>
+      <c r="AI8" s="17"/>
+      <c r="AJ8" s="17"/>
+      <c r="AK8" s="14"/>
+      <c r="AL8" s="14"/>
+    </row>
+    <row r="9" spans="1:39">
       <c r="A9" s="2">
         <v>3</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
-      <c r="F9" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F9" s="2"/>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
@@ -1568,10 +1923,7 @@
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>
-      <c r="N9" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="N9" s="4"/>
       <c r="O9" s="4"/>
       <c r="P9" s="4"/>
       <c r="Q9" s="4"/>
@@ -1584,20 +1936,30 @@
       <c r="X9" s="5"/>
       <c r="Y9" s="5"/>
       <c r="Z9" s="5"/>
-    </row>
-    <row r="10" spans="1:26">
+      <c r="AA9" s="13"/>
+      <c r="AB9" s="13"/>
+      <c r="AC9" s="16"/>
+      <c r="AD9" s="16"/>
+      <c r="AE9" s="16"/>
+      <c r="AF9" s="17"/>
+      <c r="AG9" s="16"/>
+      <c r="AH9" s="17"/>
+      <c r="AI9" s="17"/>
+      <c r="AJ9" s="17"/>
+      <c r="AK9" s="14"/>
+      <c r="AL9" s="14"/>
+    </row>
+    <row r="10" spans="1:39">
       <c r="A10" s="2">
         <v>4</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
-      <c r="F10" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F10" s="2"/>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
@@ -1605,10 +1967,7 @@
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
       <c r="M10" s="4"/>
-      <c r="N10" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="N10" s="4"/>
       <c r="O10" s="4"/>
       <c r="P10" s="4"/>
       <c r="Q10" s="4"/>
@@ -1621,20 +1980,30 @@
       <c r="X10" s="5"/>
       <c r="Y10" s="5"/>
       <c r="Z10" s="5"/>
-    </row>
-    <row r="11" spans="1:26">
+      <c r="AA10" s="13"/>
+      <c r="AB10" s="13"/>
+      <c r="AC10" s="16"/>
+      <c r="AD10" s="16"/>
+      <c r="AE10" s="16"/>
+      <c r="AF10" s="17"/>
+      <c r="AG10" s="16"/>
+      <c r="AH10" s="17"/>
+      <c r="AI10" s="17"/>
+      <c r="AJ10" s="17"/>
+      <c r="AK10" s="14"/>
+      <c r="AL10" s="14"/>
+    </row>
+    <row r="11" spans="1:39">
       <c r="A11" s="2">
         <v>5</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
-      <c r="F11" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F11" s="2"/>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
@@ -1642,10 +2011,7 @@
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
       <c r="M11" s="4"/>
-      <c r="N11" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="N11" s="4"/>
       <c r="O11" s="4"/>
       <c r="P11" s="4"/>
       <c r="Q11" s="4"/>
@@ -1658,20 +2024,30 @@
       <c r="X11" s="5"/>
       <c r="Y11" s="5"/>
       <c r="Z11" s="5"/>
-    </row>
-    <row r="12" spans="1:26">
+      <c r="AA11" s="13"/>
+      <c r="AB11" s="13"/>
+      <c r="AC11" s="16"/>
+      <c r="AD11" s="16"/>
+      <c r="AE11" s="16"/>
+      <c r="AF11" s="17"/>
+      <c r="AG11" s="16"/>
+      <c r="AH11" s="17"/>
+      <c r="AI11" s="17"/>
+      <c r="AJ11" s="17"/>
+      <c r="AK11" s="14"/>
+      <c r="AL11" s="14"/>
+    </row>
+    <row r="12" spans="1:39">
       <c r="A12" s="2">
         <v>6</v>
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
-      <c r="F12" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F12" s="2"/>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
@@ -1679,10 +2055,7 @@
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
       <c r="M12" s="4"/>
-      <c r="N12" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="N12" s="4"/>
       <c r="O12" s="4"/>
       <c r="P12" s="4"/>
       <c r="Q12" s="4"/>
@@ -1695,20 +2068,30 @@
       <c r="X12" s="5"/>
       <c r="Y12" s="5"/>
       <c r="Z12" s="5"/>
-    </row>
-    <row r="13" spans="1:26">
+      <c r="AA12" s="13"/>
+      <c r="AB12" s="13"/>
+      <c r="AC12" s="16"/>
+      <c r="AD12" s="16"/>
+      <c r="AE12" s="16"/>
+      <c r="AF12" s="17"/>
+      <c r="AG12" s="16"/>
+      <c r="AH12" s="17"/>
+      <c r="AI12" s="17"/>
+      <c r="AJ12" s="17"/>
+      <c r="AK12" s="14"/>
+      <c r="AL12" s="14"/>
+    </row>
+    <row r="13" spans="1:39">
       <c r="A13" s="2">
         <v>7</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
-      <c r="F13" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F13" s="2"/>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
@@ -1716,10 +2099,7 @@
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
       <c r="M13" s="4"/>
-      <c r="N13" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="N13" s="4"/>
       <c r="O13" s="4"/>
       <c r="P13" s="4"/>
       <c r="Q13" s="4"/>
@@ -1732,20 +2112,30 @@
       <c r="X13" s="5"/>
       <c r="Y13" s="5"/>
       <c r="Z13" s="5"/>
-    </row>
-    <row r="14" spans="1:26">
+      <c r="AA13" s="13"/>
+      <c r="AB13" s="13"/>
+      <c r="AC13" s="16"/>
+      <c r="AD13" s="16"/>
+      <c r="AE13" s="16"/>
+      <c r="AF13" s="17"/>
+      <c r="AG13" s="16"/>
+      <c r="AH13" s="17"/>
+      <c r="AI13" s="17"/>
+      <c r="AJ13" s="17"/>
+      <c r="AK13" s="14"/>
+      <c r="AL13" s="14"/>
+    </row>
+    <row r="14" spans="1:39">
       <c r="A14" s="2">
         <v>8</v>
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
-      <c r="F14" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F14" s="2"/>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
@@ -1754,7 +2144,7 @@
       <c r="L14" s="4"/>
       <c r="M14" s="4"/>
       <c r="N14" s="4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="N7:N38" si="0">IF(AND(K14&lt;&gt;"",L14&lt;&gt;"",M14&lt;&gt;""),K14+L14+M14,"")</f>
         <v/>
       </c>
       <c r="O14" s="4"/>
@@ -1769,20 +2159,30 @@
       <c r="X14" s="5"/>
       <c r="Y14" s="5"/>
       <c r="Z14" s="5"/>
-    </row>
-    <row r="15" spans="1:26">
+      <c r="AA14" s="13"/>
+      <c r="AB14" s="13"/>
+      <c r="AC14" s="16"/>
+      <c r="AD14" s="16"/>
+      <c r="AE14" s="16"/>
+      <c r="AF14" s="17"/>
+      <c r="AG14" s="16"/>
+      <c r="AH14" s="17"/>
+      <c r="AI14" s="17"/>
+      <c r="AJ14" s="17"/>
+      <c r="AK14" s="14"/>
+      <c r="AL14" s="14"/>
+    </row>
+    <row r="15" spans="1:39">
       <c r="A15" s="2">
         <v>9</v>
       </c>
       <c r="B15" s="3"/>
       <c r="C15" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
-      <c r="F15" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F15" s="2"/>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
@@ -1806,20 +2206,30 @@
       <c r="X15" s="5"/>
       <c r="Y15" s="5"/>
       <c r="Z15" s="5"/>
-    </row>
-    <row r="16" spans="1:26">
+      <c r="AA15" s="13"/>
+      <c r="AB15" s="13"/>
+      <c r="AC15" s="16"/>
+      <c r="AD15" s="16"/>
+      <c r="AE15" s="16"/>
+      <c r="AF15" s="17"/>
+      <c r="AG15" s="16"/>
+      <c r="AH15" s="17"/>
+      <c r="AI15" s="17"/>
+      <c r="AJ15" s="17"/>
+      <c r="AK15" s="14"/>
+      <c r="AL15" s="14"/>
+    </row>
+    <row r="16" spans="1:39">
       <c r="A16" s="2">
         <v>10</v>
       </c>
       <c r="B16" s="3"/>
       <c r="C16" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
-      <c r="F16" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F16" s="2"/>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
@@ -1843,20 +2253,30 @@
       <c r="X16" s="5"/>
       <c r="Y16" s="5"/>
       <c r="Z16" s="5"/>
-    </row>
-    <row r="17" spans="1:26">
+      <c r="AA16" s="13"/>
+      <c r="AB16" s="13"/>
+      <c r="AC16" s="16"/>
+      <c r="AD16" s="16"/>
+      <c r="AE16" s="16"/>
+      <c r="AF16" s="17"/>
+      <c r="AG16" s="16"/>
+      <c r="AH16" s="17"/>
+      <c r="AI16" s="17"/>
+      <c r="AJ16" s="17"/>
+      <c r="AK16" s="14"/>
+      <c r="AL16" s="14"/>
+    </row>
+    <row r="17" spans="1:38">
       <c r="A17" s="2">
         <v>11</v>
       </c>
       <c r="B17" s="3"/>
       <c r="C17" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
-      <c r="F17" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F17" s="2"/>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
@@ -1880,20 +2300,30 @@
       <c r="X17" s="5"/>
       <c r="Y17" s="5"/>
       <c r="Z17" s="5"/>
-    </row>
-    <row r="18" spans="1:26">
+      <c r="AA17" s="13"/>
+      <c r="AB17" s="13"/>
+      <c r="AC17" s="16"/>
+      <c r="AD17" s="16"/>
+      <c r="AE17" s="16"/>
+      <c r="AF17" s="17"/>
+      <c r="AG17" s="16"/>
+      <c r="AH17" s="17"/>
+      <c r="AI17" s="17"/>
+      <c r="AJ17" s="17"/>
+      <c r="AK17" s="14"/>
+      <c r="AL17" s="14"/>
+    </row>
+    <row r="18" spans="1:38">
       <c r="A18" s="2">
         <v>12</v>
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
-      <c r="F18" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F18" s="2"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
@@ -1917,20 +2347,30 @@
       <c r="X18" s="5"/>
       <c r="Y18" s="5"/>
       <c r="Z18" s="5"/>
-    </row>
-    <row r="19" spans="1:26">
+      <c r="AA18" s="13"/>
+      <c r="AB18" s="13"/>
+      <c r="AC18" s="16"/>
+      <c r="AD18" s="16"/>
+      <c r="AE18" s="16"/>
+      <c r="AF18" s="17"/>
+      <c r="AG18" s="16"/>
+      <c r="AH18" s="17"/>
+      <c r="AI18" s="17"/>
+      <c r="AJ18" s="17"/>
+      <c r="AK18" s="14"/>
+      <c r="AL18" s="14"/>
+    </row>
+    <row r="19" spans="1:38">
       <c r="A19" s="2">
         <v>13</v>
       </c>
       <c r="B19" s="3"/>
       <c r="C19" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
-      <c r="F19" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F19" s="2"/>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
@@ -1954,20 +2394,30 @@
       <c r="X19" s="5"/>
       <c r="Y19" s="5"/>
       <c r="Z19" s="5"/>
-    </row>
-    <row r="20" spans="1:26">
+      <c r="AA19" s="13"/>
+      <c r="AB19" s="13"/>
+      <c r="AC19" s="16"/>
+      <c r="AD19" s="16"/>
+      <c r="AE19" s="16"/>
+      <c r="AF19" s="17"/>
+      <c r="AG19" s="16"/>
+      <c r="AH19" s="17"/>
+      <c r="AI19" s="17"/>
+      <c r="AJ19" s="17"/>
+      <c r="AK19" s="14"/>
+      <c r="AL19" s="14"/>
+    </row>
+    <row r="20" spans="1:38">
       <c r="A20" s="2">
         <v>14</v>
       </c>
       <c r="B20" s="3"/>
       <c r="C20" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
-      <c r="F20" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F20" s="2"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
@@ -1991,20 +2441,30 @@
       <c r="X20" s="5"/>
       <c r="Y20" s="5"/>
       <c r="Z20" s="5"/>
-    </row>
-    <row r="21" spans="1:26">
+      <c r="AA20" s="13"/>
+      <c r="AB20" s="13"/>
+      <c r="AC20" s="16"/>
+      <c r="AD20" s="16"/>
+      <c r="AE20" s="16"/>
+      <c r="AF20" s="17"/>
+      <c r="AG20" s="16"/>
+      <c r="AH20" s="17"/>
+      <c r="AI20" s="17"/>
+      <c r="AJ20" s="17"/>
+      <c r="AK20" s="14"/>
+      <c r="AL20" s="14"/>
+    </row>
+    <row r="21" spans="1:38">
       <c r="A21" s="2">
         <v>15</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
-      <c r="F21" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F21" s="2"/>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
@@ -2028,20 +2488,30 @@
       <c r="X21" s="5"/>
       <c r="Y21" s="5"/>
       <c r="Z21" s="5"/>
-    </row>
-    <row r="22" spans="1:26">
+      <c r="AA21" s="13"/>
+      <c r="AB21" s="13"/>
+      <c r="AC21" s="16"/>
+      <c r="AD21" s="16"/>
+      <c r="AE21" s="16"/>
+      <c r="AF21" s="17"/>
+      <c r="AG21" s="16"/>
+      <c r="AH21" s="17"/>
+      <c r="AI21" s="17"/>
+      <c r="AJ21" s="17"/>
+      <c r="AK21" s="14"/>
+      <c r="AL21" s="14"/>
+    </row>
+    <row r="22" spans="1:38">
       <c r="A22" s="2">
         <v>16</v>
       </c>
       <c r="B22" s="3"/>
       <c r="C22" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
-      <c r="F22" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F22" s="2"/>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
@@ -2065,20 +2535,30 @@
       <c r="X22" s="5"/>
       <c r="Y22" s="5"/>
       <c r="Z22" s="5"/>
-    </row>
-    <row r="23" spans="1:26">
+      <c r="AA22" s="13"/>
+      <c r="AB22" s="13"/>
+      <c r="AC22" s="16"/>
+      <c r="AD22" s="16"/>
+      <c r="AE22" s="16"/>
+      <c r="AF22" s="17"/>
+      <c r="AG22" s="16"/>
+      <c r="AH22" s="17"/>
+      <c r="AI22" s="17"/>
+      <c r="AJ22" s="17"/>
+      <c r="AK22" s="14"/>
+      <c r="AL22" s="14"/>
+    </row>
+    <row r="23" spans="1:38">
       <c r="A23" s="2">
         <v>17</v>
       </c>
       <c r="B23" s="3"/>
       <c r="C23" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
-      <c r="F23" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F23" s="2"/>
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
@@ -2102,20 +2582,30 @@
       <c r="X23" s="5"/>
       <c r="Y23" s="5"/>
       <c r="Z23" s="5"/>
-    </row>
-    <row r="24" spans="1:26">
+      <c r="AA23" s="13"/>
+      <c r="AB23" s="13"/>
+      <c r="AC23" s="16"/>
+      <c r="AD23" s="16"/>
+      <c r="AE23" s="16"/>
+      <c r="AF23" s="17"/>
+      <c r="AG23" s="16"/>
+      <c r="AH23" s="17"/>
+      <c r="AI23" s="17"/>
+      <c r="AJ23" s="17"/>
+      <c r="AK23" s="14"/>
+      <c r="AL23" s="14"/>
+    </row>
+    <row r="24" spans="1:38">
       <c r="A24" s="2">
         <v>18</v>
       </c>
       <c r="B24" s="3"/>
       <c r="C24" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
-      <c r="F24" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F24" s="2"/>
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
@@ -2139,20 +2629,30 @@
       <c r="X24" s="5"/>
       <c r="Y24" s="5"/>
       <c r="Z24" s="5"/>
-    </row>
-    <row r="25" spans="1:26">
+      <c r="AA24" s="13"/>
+      <c r="AB24" s="13"/>
+      <c r="AC24" s="16"/>
+      <c r="AD24" s="16"/>
+      <c r="AE24" s="16"/>
+      <c r="AF24" s="17"/>
+      <c r="AG24" s="16"/>
+      <c r="AH24" s="17"/>
+      <c r="AI24" s="17"/>
+      <c r="AJ24" s="17"/>
+      <c r="AK24" s="14"/>
+      <c r="AL24" s="14"/>
+    </row>
+    <row r="25" spans="1:38">
       <c r="A25" s="2">
         <v>19</v>
       </c>
       <c r="B25" s="3"/>
       <c r="C25" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D25" s="2"/>
       <c r="E25" s="2"/>
-      <c r="F25" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F25" s="2"/>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
@@ -2176,20 +2676,30 @@
       <c r="X25" s="5"/>
       <c r="Y25" s="5"/>
       <c r="Z25" s="5"/>
-    </row>
-    <row r="26" spans="1:26">
+      <c r="AA25" s="13"/>
+      <c r="AB25" s="13"/>
+      <c r="AC25" s="16"/>
+      <c r="AD25" s="16"/>
+      <c r="AE25" s="16"/>
+      <c r="AF25" s="17"/>
+      <c r="AG25" s="16"/>
+      <c r="AH25" s="17"/>
+      <c r="AI25" s="17"/>
+      <c r="AJ25" s="17"/>
+      <c r="AK25" s="14"/>
+      <c r="AL25" s="14"/>
+    </row>
+    <row r="26" spans="1:38">
       <c r="A26" s="2">
         <v>20</v>
       </c>
       <c r="B26" s="3"/>
       <c r="C26" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D26" s="2"/>
       <c r="E26" s="2"/>
-      <c r="F26" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F26" s="2"/>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
@@ -2213,20 +2723,30 @@
       <c r="X26" s="5"/>
       <c r="Y26" s="5"/>
       <c r="Z26" s="5"/>
-    </row>
-    <row r="27" spans="1:26">
+      <c r="AA26" s="13"/>
+      <c r="AB26" s="13"/>
+      <c r="AC26" s="16"/>
+      <c r="AD26" s="16"/>
+      <c r="AE26" s="16"/>
+      <c r="AF26" s="17"/>
+      <c r="AG26" s="16"/>
+      <c r="AH26" s="17"/>
+      <c r="AI26" s="17"/>
+      <c r="AJ26" s="17"/>
+      <c r="AK26" s="14"/>
+      <c r="AL26" s="14"/>
+    </row>
+    <row r="27" spans="1:38">
       <c r="A27" s="2">
         <v>21</v>
       </c>
       <c r="B27" s="3"/>
       <c r="C27" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D27" s="2"/>
       <c r="E27" s="2"/>
-      <c r="F27" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F27" s="2"/>
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
@@ -2250,20 +2770,30 @@
       <c r="X27" s="5"/>
       <c r="Y27" s="5"/>
       <c r="Z27" s="5"/>
-    </row>
-    <row r="28" spans="1:26">
+      <c r="AA27" s="13"/>
+      <c r="AB27" s="13"/>
+      <c r="AC27" s="16"/>
+      <c r="AD27" s="16"/>
+      <c r="AE27" s="16"/>
+      <c r="AF27" s="17"/>
+      <c r="AG27" s="16"/>
+      <c r="AH27" s="17"/>
+      <c r="AI27" s="17"/>
+      <c r="AJ27" s="17"/>
+      <c r="AK27" s="14"/>
+      <c r="AL27" s="14"/>
+    </row>
+    <row r="28" spans="1:38">
       <c r="A28" s="2">
         <v>22</v>
       </c>
       <c r="B28" s="3"/>
       <c r="C28" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" s="2"/>
-      <c r="F28" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F28" s="2"/>
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
       <c r="I28" s="2"/>
@@ -2287,20 +2817,30 @@
       <c r="X28" s="5"/>
       <c r="Y28" s="5"/>
       <c r="Z28" s="5"/>
-    </row>
-    <row r="29" spans="1:26">
+      <c r="AA28" s="13"/>
+      <c r="AB28" s="13"/>
+      <c r="AC28" s="16"/>
+      <c r="AD28" s="16"/>
+      <c r="AE28" s="16"/>
+      <c r="AF28" s="17"/>
+      <c r="AG28" s="16"/>
+      <c r="AH28" s="17"/>
+      <c r="AI28" s="17"/>
+      <c r="AJ28" s="17"/>
+      <c r="AK28" s="14"/>
+      <c r="AL28" s="14"/>
+    </row>
+    <row r="29" spans="1:38">
       <c r="A29" s="2">
         <v>23</v>
       </c>
       <c r="B29" s="3"/>
       <c r="C29" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D29" s="2"/>
       <c r="E29" s="2"/>
-      <c r="F29" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F29" s="2"/>
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
@@ -2324,20 +2864,30 @@
       <c r="X29" s="5"/>
       <c r="Y29" s="5"/>
       <c r="Z29" s="5"/>
-    </row>
-    <row r="30" spans="1:26">
+      <c r="AA29" s="13"/>
+      <c r="AB29" s="13"/>
+      <c r="AC29" s="16"/>
+      <c r="AD29" s="16"/>
+      <c r="AE29" s="16"/>
+      <c r="AF29" s="17"/>
+      <c r="AG29" s="16"/>
+      <c r="AH29" s="17"/>
+      <c r="AI29" s="17"/>
+      <c r="AJ29" s="17"/>
+      <c r="AK29" s="14"/>
+      <c r="AL29" s="14"/>
+    </row>
+    <row r="30" spans="1:38">
       <c r="A30" s="2">
         <v>24</v>
       </c>
       <c r="B30" s="3"/>
       <c r="C30" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
-      <c r="F30" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F30" s="2"/>
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
@@ -2361,20 +2911,30 @@
       <c r="X30" s="5"/>
       <c r="Y30" s="5"/>
       <c r="Z30" s="5"/>
-    </row>
-    <row r="31" spans="1:26">
+      <c r="AA30" s="13"/>
+      <c r="AB30" s="13"/>
+      <c r="AC30" s="16"/>
+      <c r="AD30" s="16"/>
+      <c r="AE30" s="16"/>
+      <c r="AF30" s="17"/>
+      <c r="AG30" s="16"/>
+      <c r="AH30" s="17"/>
+      <c r="AI30" s="17"/>
+      <c r="AJ30" s="17"/>
+      <c r="AK30" s="14"/>
+      <c r="AL30" s="14"/>
+    </row>
+    <row r="31" spans="1:38">
       <c r="A31" s="2">
         <v>25</v>
       </c>
       <c r="B31" s="3"/>
       <c r="C31" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D31" s="2"/>
       <c r="E31" s="2"/>
-      <c r="F31" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F31" s="2"/>
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
@@ -2398,20 +2958,30 @@
       <c r="X31" s="5"/>
       <c r="Y31" s="5"/>
       <c r="Z31" s="5"/>
-    </row>
-    <row r="32" spans="1:26">
+      <c r="AA31" s="13"/>
+      <c r="AB31" s="13"/>
+      <c r="AC31" s="16"/>
+      <c r="AD31" s="16"/>
+      <c r="AE31" s="16"/>
+      <c r="AF31" s="17"/>
+      <c r="AG31" s="16"/>
+      <c r="AH31" s="17"/>
+      <c r="AI31" s="17"/>
+      <c r="AJ31" s="17"/>
+      <c r="AK31" s="14"/>
+      <c r="AL31" s="14"/>
+    </row>
+    <row r="32" spans="1:38">
       <c r="A32" s="2">
         <v>26</v>
       </c>
       <c r="B32" s="3"/>
       <c r="C32" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D32" s="2"/>
       <c r="E32" s="2"/>
-      <c r="F32" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F32" s="2"/>
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
       <c r="I32" s="2"/>
@@ -2435,20 +3005,30 @@
       <c r="X32" s="5"/>
       <c r="Y32" s="5"/>
       <c r="Z32" s="5"/>
-    </row>
-    <row r="33" spans="1:26">
+      <c r="AA32" s="13"/>
+      <c r="AB32" s="13"/>
+      <c r="AC32" s="16"/>
+      <c r="AD32" s="16"/>
+      <c r="AE32" s="16"/>
+      <c r="AF32" s="17"/>
+      <c r="AG32" s="16"/>
+      <c r="AH32" s="17"/>
+      <c r="AI32" s="17"/>
+      <c r="AJ32" s="17"/>
+      <c r="AK32" s="14"/>
+      <c r="AL32" s="14"/>
+    </row>
+    <row r="33" spans="1:38">
       <c r="A33" s="2">
         <v>27</v>
       </c>
       <c r="B33" s="3"/>
       <c r="C33" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D33" s="2"/>
       <c r="E33" s="2"/>
-      <c r="F33" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F33" s="2"/>
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
       <c r="I33" s="2"/>
@@ -2472,20 +3052,30 @@
       <c r="X33" s="5"/>
       <c r="Y33" s="5"/>
       <c r="Z33" s="5"/>
-    </row>
-    <row r="34" spans="1:26">
+      <c r="AA33" s="13"/>
+      <c r="AB33" s="13"/>
+      <c r="AC33" s="16"/>
+      <c r="AD33" s="16"/>
+      <c r="AE33" s="16"/>
+      <c r="AF33" s="17"/>
+      <c r="AG33" s="16"/>
+      <c r="AH33" s="17"/>
+      <c r="AI33" s="17"/>
+      <c r="AJ33" s="17"/>
+      <c r="AK33" s="14"/>
+      <c r="AL33" s="14"/>
+    </row>
+    <row r="34" spans="1:38">
       <c r="A34" s="2">
         <v>28</v>
       </c>
       <c r="B34" s="3"/>
       <c r="C34" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" s="2"/>
-      <c r="F34" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F34" s="2"/>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
       <c r="I34" s="2"/>
@@ -2509,20 +3099,30 @@
       <c r="X34" s="5"/>
       <c r="Y34" s="5"/>
       <c r="Z34" s="5"/>
-    </row>
-    <row r="35" spans="1:26">
+      <c r="AA34" s="13"/>
+      <c r="AB34" s="13"/>
+      <c r="AC34" s="16"/>
+      <c r="AD34" s="16"/>
+      <c r="AE34" s="16"/>
+      <c r="AF34" s="17"/>
+      <c r="AG34" s="16"/>
+      <c r="AH34" s="17"/>
+      <c r="AI34" s="17"/>
+      <c r="AJ34" s="17"/>
+      <c r="AK34" s="14"/>
+      <c r="AL34" s="14"/>
+    </row>
+    <row r="35" spans="1:38">
       <c r="A35" s="2">
         <v>29</v>
       </c>
       <c r="B35" s="3"/>
       <c r="C35" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D35" s="2"/>
       <c r="E35" s="2"/>
-      <c r="F35" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F35" s="2"/>
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
       <c r="I35" s="2"/>
@@ -2546,20 +3146,30 @@
       <c r="X35" s="5"/>
       <c r="Y35" s="5"/>
       <c r="Z35" s="5"/>
-    </row>
-    <row r="36" spans="1:26">
+      <c r="AA35" s="13"/>
+      <c r="AB35" s="13"/>
+      <c r="AC35" s="16"/>
+      <c r="AD35" s="16"/>
+      <c r="AE35" s="16"/>
+      <c r="AF35" s="17"/>
+      <c r="AG35" s="16"/>
+      <c r="AH35" s="17"/>
+      <c r="AI35" s="17"/>
+      <c r="AJ35" s="17"/>
+      <c r="AK35" s="14"/>
+      <c r="AL35" s="14"/>
+    </row>
+    <row r="36" spans="1:38">
       <c r="A36" s="2">
         <v>30</v>
       </c>
       <c r="B36" s="3"/>
       <c r="C36" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D36" s="2"/>
       <c r="E36" s="2"/>
-      <c r="F36" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F36" s="2"/>
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
       <c r="I36" s="2"/>
@@ -2583,20 +3193,30 @@
       <c r="X36" s="5"/>
       <c r="Y36" s="5"/>
       <c r="Z36" s="5"/>
-    </row>
-    <row r="37" spans="1:26">
+      <c r="AA36" s="13"/>
+      <c r="AB36" s="13"/>
+      <c r="AC36" s="16"/>
+      <c r="AD36" s="16"/>
+      <c r="AE36" s="16"/>
+      <c r="AF36" s="17"/>
+      <c r="AG36" s="16"/>
+      <c r="AH36" s="17"/>
+      <c r="AI36" s="17"/>
+      <c r="AJ36" s="17"/>
+      <c r="AK36" s="14"/>
+      <c r="AL36" s="14"/>
+    </row>
+    <row r="37" spans="1:38">
       <c r="A37" s="2">
         <v>31</v>
       </c>
       <c r="B37" s="3"/>
       <c r="C37" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" s="2"/>
-      <c r="F37" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F37" s="2"/>
       <c r="G37" s="2"/>
       <c r="H37" s="2"/>
       <c r="I37" s="2"/>
@@ -2620,20 +3240,30 @@
       <c r="X37" s="5"/>
       <c r="Y37" s="5"/>
       <c r="Z37" s="5"/>
-    </row>
-    <row r="38" spans="1:26">
+      <c r="AA37" s="13"/>
+      <c r="AB37" s="13"/>
+      <c r="AC37" s="16"/>
+      <c r="AD37" s="16"/>
+      <c r="AE37" s="16"/>
+      <c r="AF37" s="17"/>
+      <c r="AG37" s="16"/>
+      <c r="AH37" s="17"/>
+      <c r="AI37" s="17"/>
+      <c r="AJ37" s="17"/>
+      <c r="AK37" s="14"/>
+      <c r="AL37" s="14"/>
+    </row>
+    <row r="38" spans="1:38">
       <c r="A38" s="2">
         <v>32</v>
       </c>
       <c r="B38" s="3"/>
       <c r="C38" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D38" s="2"/>
       <c r="E38" s="2"/>
-      <c r="F38" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F38" s="2"/>
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
       <c r="I38" s="2"/>
@@ -2657,20 +3287,30 @@
       <c r="X38" s="5"/>
       <c r="Y38" s="5"/>
       <c r="Z38" s="5"/>
-    </row>
-    <row r="39" spans="1:26">
+      <c r="AA38" s="13"/>
+      <c r="AB38" s="13"/>
+      <c r="AC38" s="16"/>
+      <c r="AD38" s="16"/>
+      <c r="AE38" s="16"/>
+      <c r="AF38" s="17"/>
+      <c r="AG38" s="16"/>
+      <c r="AH38" s="17"/>
+      <c r="AI38" s="17"/>
+      <c r="AJ38" s="17"/>
+      <c r="AK38" s="14"/>
+      <c r="AL38" s="14"/>
+    </row>
+    <row r="39" spans="1:38">
       <c r="A39" s="2">
         <v>33</v>
       </c>
       <c r="B39" s="3"/>
       <c r="C39" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" s="2"/>
-      <c r="F39" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F39" s="2"/>
       <c r="G39" s="2"/>
       <c r="H39" s="2"/>
       <c r="I39" s="2"/>
@@ -2694,20 +3334,30 @@
       <c r="X39" s="5"/>
       <c r="Y39" s="5"/>
       <c r="Z39" s="5"/>
-    </row>
-    <row r="40" spans="1:26">
+      <c r="AA39" s="13"/>
+      <c r="AB39" s="13"/>
+      <c r="AC39" s="16"/>
+      <c r="AD39" s="16"/>
+      <c r="AE39" s="16"/>
+      <c r="AF39" s="17"/>
+      <c r="AG39" s="16"/>
+      <c r="AH39" s="17"/>
+      <c r="AI39" s="17"/>
+      <c r="AJ39" s="17"/>
+      <c r="AK39" s="14"/>
+      <c r="AL39" s="14"/>
+    </row>
+    <row r="40" spans="1:38">
       <c r="A40" s="2">
         <v>34</v>
       </c>
       <c r="B40" s="3"/>
       <c r="C40" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D40" s="2"/>
       <c r="E40" s="2"/>
-      <c r="F40" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F40" s="2"/>
       <c r="G40" s="2"/>
       <c r="H40" s="2"/>
       <c r="I40" s="2"/>
@@ -2731,20 +3381,30 @@
       <c r="X40" s="5"/>
       <c r="Y40" s="5"/>
       <c r="Z40" s="5"/>
-    </row>
-    <row r="41" spans="1:26">
+      <c r="AA40" s="13"/>
+      <c r="AB40" s="13"/>
+      <c r="AC40" s="16"/>
+      <c r="AD40" s="16"/>
+      <c r="AE40" s="16"/>
+      <c r="AF40" s="17"/>
+      <c r="AG40" s="16"/>
+      <c r="AH40" s="17"/>
+      <c r="AI40" s="17"/>
+      <c r="AJ40" s="17"/>
+      <c r="AK40" s="14"/>
+      <c r="AL40" s="14"/>
+    </row>
+    <row r="41" spans="1:38">
       <c r="A41" s="2">
         <v>35</v>
       </c>
       <c r="B41" s="3"/>
       <c r="C41" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D41" s="2"/>
       <c r="E41" s="2"/>
-      <c r="F41" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F41" s="2"/>
       <c r="G41" s="2"/>
       <c r="H41" s="2"/>
       <c r="I41" s="2"/>
@@ -2768,20 +3428,30 @@
       <c r="X41" s="5"/>
       <c r="Y41" s="5"/>
       <c r="Z41" s="5"/>
-    </row>
-    <row r="42" spans="1:26">
+      <c r="AA41" s="13"/>
+      <c r="AB41" s="13"/>
+      <c r="AC41" s="16"/>
+      <c r="AD41" s="16"/>
+      <c r="AE41" s="16"/>
+      <c r="AF41" s="17"/>
+      <c r="AG41" s="16"/>
+      <c r="AH41" s="17"/>
+      <c r="AI41" s="17"/>
+      <c r="AJ41" s="17"/>
+      <c r="AK41" s="14"/>
+      <c r="AL41" s="14"/>
+    </row>
+    <row r="42" spans="1:38">
       <c r="A42" s="2">
         <v>36</v>
       </c>
       <c r="B42" s="3"/>
       <c r="C42" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D42" s="2"/>
       <c r="E42" s="2"/>
-      <c r="F42" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F42" s="2"/>
       <c r="G42" s="2"/>
       <c r="H42" s="2"/>
       <c r="I42" s="2"/>
@@ -2805,20 +3475,30 @@
       <c r="X42" s="5"/>
       <c r="Y42" s="5"/>
       <c r="Z42" s="5"/>
-    </row>
-    <row r="43" spans="1:26">
+      <c r="AA42" s="13"/>
+      <c r="AB42" s="13"/>
+      <c r="AC42" s="16"/>
+      <c r="AD42" s="16"/>
+      <c r="AE42" s="16"/>
+      <c r="AF42" s="17"/>
+      <c r="AG42" s="16"/>
+      <c r="AH42" s="17"/>
+      <c r="AI42" s="17"/>
+      <c r="AJ42" s="17"/>
+      <c r="AK42" s="14"/>
+      <c r="AL42" s="14"/>
+    </row>
+    <row r="43" spans="1:38">
       <c r="A43" s="2">
         <v>37</v>
       </c>
       <c r="B43" s="3"/>
       <c r="C43" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D43" s="2"/>
       <c r="E43" s="2"/>
-      <c r="F43" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F43" s="2"/>
       <c r="G43" s="2"/>
       <c r="H43" s="2"/>
       <c r="I43" s="2"/>
@@ -2842,20 +3522,30 @@
       <c r="X43" s="5"/>
       <c r="Y43" s="5"/>
       <c r="Z43" s="5"/>
-    </row>
-    <row r="44" spans="1:26">
+      <c r="AA43" s="13"/>
+      <c r="AB43" s="13"/>
+      <c r="AC43" s="16"/>
+      <c r="AD43" s="16"/>
+      <c r="AE43" s="16"/>
+      <c r="AF43" s="17"/>
+      <c r="AG43" s="16"/>
+      <c r="AH43" s="17"/>
+      <c r="AI43" s="17"/>
+      <c r="AJ43" s="17"/>
+      <c r="AK43" s="14"/>
+      <c r="AL43" s="14"/>
+    </row>
+    <row r="44" spans="1:38">
       <c r="A44" s="2">
         <v>38</v>
       </c>
       <c r="B44" s="3"/>
       <c r="C44" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D44" s="2"/>
       <c r="E44" s="2"/>
-      <c r="F44" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F44" s="2"/>
       <c r="G44" s="2"/>
       <c r="H44" s="2"/>
       <c r="I44" s="2"/>
@@ -2879,20 +3569,30 @@
       <c r="X44" s="5"/>
       <c r="Y44" s="5"/>
       <c r="Z44" s="5"/>
-    </row>
-    <row r="45" spans="1:26">
+      <c r="AA44" s="13"/>
+      <c r="AB44" s="13"/>
+      <c r="AC44" s="16"/>
+      <c r="AD44" s="16"/>
+      <c r="AE44" s="16"/>
+      <c r="AF44" s="17"/>
+      <c r="AG44" s="16"/>
+      <c r="AH44" s="17"/>
+      <c r="AI44" s="17"/>
+      <c r="AJ44" s="17"/>
+      <c r="AK44" s="14"/>
+      <c r="AL44" s="14"/>
+    </row>
+    <row r="45" spans="1:38">
       <c r="A45" s="2">
         <v>39</v>
       </c>
       <c r="B45" s="3"/>
       <c r="C45" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D45" s="2"/>
       <c r="E45" s="2"/>
-      <c r="F45" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F45" s="2"/>
       <c r="G45" s="2"/>
       <c r="H45" s="2"/>
       <c r="I45" s="2"/>
@@ -2916,20 +3616,30 @@
       <c r="X45" s="5"/>
       <c r="Y45" s="5"/>
       <c r="Z45" s="5"/>
-    </row>
-    <row r="46" spans="1:26">
+      <c r="AA45" s="13"/>
+      <c r="AB45" s="13"/>
+      <c r="AC45" s="16"/>
+      <c r="AD45" s="16"/>
+      <c r="AE45" s="16"/>
+      <c r="AF45" s="17"/>
+      <c r="AG45" s="16"/>
+      <c r="AH45" s="17"/>
+      <c r="AI45" s="17"/>
+      <c r="AJ45" s="17"/>
+      <c r="AK45" s="14"/>
+      <c r="AL45" s="14"/>
+    </row>
+    <row r="46" spans="1:38">
       <c r="A46" s="2">
         <v>40</v>
       </c>
       <c r="B46" s="3"/>
       <c r="C46" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D46" s="2"/>
       <c r="E46" s="2"/>
-      <c r="F46" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F46" s="2"/>
       <c r="G46" s="2"/>
       <c r="H46" s="2"/>
       <c r="I46" s="2"/>
@@ -2953,20 +3663,30 @@
       <c r="X46" s="5"/>
       <c r="Y46" s="5"/>
       <c r="Z46" s="5"/>
-    </row>
-    <row r="47" spans="1:26">
+      <c r="AA46" s="13"/>
+      <c r="AB46" s="13"/>
+      <c r="AC46" s="16"/>
+      <c r="AD46" s="16"/>
+      <c r="AE46" s="16"/>
+      <c r="AF46" s="17"/>
+      <c r="AG46" s="16"/>
+      <c r="AH46" s="17"/>
+      <c r="AI46" s="17"/>
+      <c r="AJ46" s="17"/>
+      <c r="AK46" s="14"/>
+      <c r="AL46" s="14"/>
+    </row>
+    <row r="47" spans="1:38">
       <c r="A47" s="2">
         <v>41</v>
       </c>
       <c r="B47" s="3"/>
       <c r="C47" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D47" s="2"/>
       <c r="E47" s="2"/>
-      <c r="F47" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F47" s="2"/>
       <c r="G47" s="2"/>
       <c r="H47" s="2"/>
       <c r="I47" s="2"/>
@@ -2990,20 +3710,30 @@
       <c r="X47" s="5"/>
       <c r="Y47" s="5"/>
       <c r="Z47" s="5"/>
-    </row>
-    <row r="48" spans="1:26">
+      <c r="AA47" s="13"/>
+      <c r="AB47" s="13"/>
+      <c r="AC47" s="16"/>
+      <c r="AD47" s="16"/>
+      <c r="AE47" s="16"/>
+      <c r="AF47" s="17"/>
+      <c r="AG47" s="16"/>
+      <c r="AH47" s="17"/>
+      <c r="AI47" s="17"/>
+      <c r="AJ47" s="17"/>
+      <c r="AK47" s="14"/>
+      <c r="AL47" s="14"/>
+    </row>
+    <row r="48" spans="1:38">
       <c r="A48" s="2">
         <v>42</v>
       </c>
       <c r="B48" s="3"/>
       <c r="C48" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D48" s="2"/>
       <c r="E48" s="2"/>
-      <c r="F48" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F48" s="2"/>
       <c r="G48" s="2"/>
       <c r="H48" s="2"/>
       <c r="I48" s="2"/>
@@ -3027,20 +3757,30 @@
       <c r="X48" s="5"/>
       <c r="Y48" s="5"/>
       <c r="Z48" s="5"/>
-    </row>
-    <row r="49" spans="1:26">
+      <c r="AA48" s="13"/>
+      <c r="AB48" s="13"/>
+      <c r="AC48" s="16"/>
+      <c r="AD48" s="16"/>
+      <c r="AE48" s="16"/>
+      <c r="AF48" s="17"/>
+      <c r="AG48" s="16"/>
+      <c r="AH48" s="17"/>
+      <c r="AI48" s="17"/>
+      <c r="AJ48" s="17"/>
+      <c r="AK48" s="14"/>
+      <c r="AL48" s="14"/>
+    </row>
+    <row r="49" spans="1:38">
       <c r="A49" s="2">
         <v>43</v>
       </c>
       <c r="B49" s="3"/>
       <c r="C49" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D49" s="2"/>
       <c r="E49" s="2"/>
-      <c r="F49" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F49" s="2"/>
       <c r="G49" s="2"/>
       <c r="H49" s="2"/>
       <c r="I49" s="2"/>
@@ -3064,20 +3804,30 @@
       <c r="X49" s="5"/>
       <c r="Y49" s="5"/>
       <c r="Z49" s="5"/>
-    </row>
-    <row r="50" spans="1:26">
+      <c r="AA49" s="13"/>
+      <c r="AB49" s="13"/>
+      <c r="AC49" s="16"/>
+      <c r="AD49" s="16"/>
+      <c r="AE49" s="16"/>
+      <c r="AF49" s="17"/>
+      <c r="AG49" s="16"/>
+      <c r="AH49" s="17"/>
+      <c r="AI49" s="17"/>
+      <c r="AJ49" s="17"/>
+      <c r="AK49" s="14"/>
+      <c r="AL49" s="14"/>
+    </row>
+    <row r="50" spans="1:38">
       <c r="A50" s="2">
         <v>44</v>
       </c>
       <c r="B50" s="3"/>
       <c r="C50" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D50" s="2"/>
       <c r="E50" s="2"/>
-      <c r="F50" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F50" s="2"/>
       <c r="G50" s="2"/>
       <c r="H50" s="2"/>
       <c r="I50" s="2"/>
@@ -3101,20 +3851,30 @@
       <c r="X50" s="5"/>
       <c r="Y50" s="5"/>
       <c r="Z50" s="5"/>
-    </row>
-    <row r="51" spans="1:26">
+      <c r="AA50" s="13"/>
+      <c r="AB50" s="13"/>
+      <c r="AC50" s="16"/>
+      <c r="AD50" s="16"/>
+      <c r="AE50" s="16"/>
+      <c r="AF50" s="17"/>
+      <c r="AG50" s="16"/>
+      <c r="AH50" s="17"/>
+      <c r="AI50" s="17"/>
+      <c r="AJ50" s="17"/>
+      <c r="AK50" s="14"/>
+      <c r="AL50" s="14"/>
+    </row>
+    <row r="51" spans="1:38">
       <c r="A51" s="2">
         <v>45</v>
       </c>
       <c r="B51" s="3"/>
       <c r="C51" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D51" s="2"/>
       <c r="E51" s="2"/>
-      <c r="F51" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F51" s="2"/>
       <c r="G51" s="2"/>
       <c r="H51" s="2"/>
       <c r="I51" s="2"/>
@@ -3138,20 +3898,30 @@
       <c r="X51" s="5"/>
       <c r="Y51" s="5"/>
       <c r="Z51" s="5"/>
-    </row>
-    <row r="52" spans="1:26">
+      <c r="AA51" s="13"/>
+      <c r="AB51" s="13"/>
+      <c r="AC51" s="16"/>
+      <c r="AD51" s="16"/>
+      <c r="AE51" s="16"/>
+      <c r="AF51" s="17"/>
+      <c r="AG51" s="16"/>
+      <c r="AH51" s="17"/>
+      <c r="AI51" s="17"/>
+      <c r="AJ51" s="17"/>
+      <c r="AK51" s="14"/>
+      <c r="AL51" s="14"/>
+    </row>
+    <row r="52" spans="1:38">
       <c r="A52" s="2">
         <v>46</v>
       </c>
       <c r="B52" s="3"/>
       <c r="C52" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D52" s="2"/>
       <c r="E52" s="2"/>
-      <c r="F52" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F52" s="2"/>
       <c r="G52" s="2"/>
       <c r="H52" s="2"/>
       <c r="I52" s="2"/>
@@ -3175,20 +3945,30 @@
       <c r="X52" s="5"/>
       <c r="Y52" s="5"/>
       <c r="Z52" s="5"/>
-    </row>
-    <row r="53" spans="1:26">
+      <c r="AA52" s="13"/>
+      <c r="AB52" s="13"/>
+      <c r="AC52" s="16"/>
+      <c r="AD52" s="16"/>
+      <c r="AE52" s="16"/>
+      <c r="AF52" s="17"/>
+      <c r="AG52" s="16"/>
+      <c r="AH52" s="17"/>
+      <c r="AI52" s="17"/>
+      <c r="AJ52" s="17"/>
+      <c r="AK52" s="14"/>
+      <c r="AL52" s="14"/>
+    </row>
+    <row r="53" spans="1:38">
       <c r="A53" s="2">
         <v>47</v>
       </c>
       <c r="B53" s="3"/>
       <c r="C53" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D53" s="2"/>
       <c r="E53" s="2"/>
-      <c r="F53" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F53" s="2"/>
       <c r="G53" s="2"/>
       <c r="H53" s="2"/>
       <c r="I53" s="2"/>
@@ -3212,20 +3992,30 @@
       <c r="X53" s="5"/>
       <c r="Y53" s="5"/>
       <c r="Z53" s="5"/>
-    </row>
-    <row r="54" spans="1:26">
+      <c r="AA53" s="13"/>
+      <c r="AB53" s="13"/>
+      <c r="AC53" s="16"/>
+      <c r="AD53" s="16"/>
+      <c r="AE53" s="16"/>
+      <c r="AF53" s="17"/>
+      <c r="AG53" s="16"/>
+      <c r="AH53" s="17"/>
+      <c r="AI53" s="17"/>
+      <c r="AJ53" s="17"/>
+      <c r="AK53" s="14"/>
+      <c r="AL53" s="14"/>
+    </row>
+    <row r="54" spans="1:38">
       <c r="A54" s="2">
         <v>48</v>
       </c>
       <c r="B54" s="3"/>
       <c r="C54" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D54" s="2"/>
       <c r="E54" s="2"/>
-      <c r="F54" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F54" s="2"/>
       <c r="G54" s="2"/>
       <c r="H54" s="2"/>
       <c r="I54" s="2"/>
@@ -3249,20 +4039,30 @@
       <c r="X54" s="5"/>
       <c r="Y54" s="5"/>
       <c r="Z54" s="5"/>
-    </row>
-    <row r="55" spans="1:26">
+      <c r="AA54" s="13"/>
+      <c r="AB54" s="13"/>
+      <c r="AC54" s="16"/>
+      <c r="AD54" s="16"/>
+      <c r="AE54" s="16"/>
+      <c r="AF54" s="17"/>
+      <c r="AG54" s="16"/>
+      <c r="AH54" s="17"/>
+      <c r="AI54" s="17"/>
+      <c r="AJ54" s="17"/>
+      <c r="AK54" s="14"/>
+      <c r="AL54" s="14"/>
+    </row>
+    <row r="55" spans="1:38">
       <c r="A55" s="2">
         <v>49</v>
       </c>
       <c r="B55" s="3"/>
       <c r="C55" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D55" s="2"/>
       <c r="E55" s="2"/>
-      <c r="F55" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F55" s="2"/>
       <c r="G55" s="2"/>
       <c r="H55" s="2"/>
       <c r="I55" s="2"/>
@@ -3286,20 +4086,30 @@
       <c r="X55" s="5"/>
       <c r="Y55" s="5"/>
       <c r="Z55" s="5"/>
-    </row>
-    <row r="56" spans="1:26">
+      <c r="AA55" s="13"/>
+      <c r="AB55" s="13"/>
+      <c r="AC55" s="16"/>
+      <c r="AD55" s="16"/>
+      <c r="AE55" s="16"/>
+      <c r="AF55" s="17"/>
+      <c r="AG55" s="16"/>
+      <c r="AH55" s="17"/>
+      <c r="AI55" s="17"/>
+      <c r="AJ55" s="17"/>
+      <c r="AK55" s="14"/>
+      <c r="AL55" s="14"/>
+    </row>
+    <row r="56" spans="1:38">
       <c r="A56" s="2">
         <v>50</v>
       </c>
       <c r="B56" s="3"/>
       <c r="C56" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D56" s="2"/>
       <c r="E56" s="2"/>
-      <c r="F56" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F56" s="2"/>
       <c r="G56" s="2"/>
       <c r="H56" s="2"/>
       <c r="I56" s="2"/>
@@ -3323,20 +4133,30 @@
       <c r="X56" s="5"/>
       <c r="Y56" s="5"/>
       <c r="Z56" s="5"/>
-    </row>
-    <row r="57" spans="1:26">
+      <c r="AA56" s="13"/>
+      <c r="AB56" s="13"/>
+      <c r="AC56" s="16"/>
+      <c r="AD56" s="16"/>
+      <c r="AE56" s="16"/>
+      <c r="AF56" s="17"/>
+      <c r="AG56" s="16"/>
+      <c r="AH56" s="17"/>
+      <c r="AI56" s="17"/>
+      <c r="AJ56" s="17"/>
+      <c r="AK56" s="14"/>
+      <c r="AL56" s="14"/>
+    </row>
+    <row r="57" spans="1:38">
       <c r="A57" s="2">
         <v>51</v>
       </c>
       <c r="B57" s="3"/>
       <c r="C57" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D57" s="2"/>
       <c r="E57" s="2"/>
-      <c r="F57" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F57" s="2"/>
       <c r="G57" s="2"/>
       <c r="H57" s="2"/>
       <c r="I57" s="2"/>
@@ -3360,20 +4180,30 @@
       <c r="X57" s="5"/>
       <c r="Y57" s="5"/>
       <c r="Z57" s="5"/>
-    </row>
-    <row r="58" spans="1:26">
+      <c r="AA57" s="13"/>
+      <c r="AB57" s="13"/>
+      <c r="AC57" s="16"/>
+      <c r="AD57" s="16"/>
+      <c r="AE57" s="16"/>
+      <c r="AF57" s="17"/>
+      <c r="AG57" s="16"/>
+      <c r="AH57" s="17"/>
+      <c r="AI57" s="17"/>
+      <c r="AJ57" s="17"/>
+      <c r="AK57" s="14"/>
+      <c r="AL57" s="14"/>
+    </row>
+    <row r="58" spans="1:38">
       <c r="A58" s="2">
         <v>52</v>
       </c>
       <c r="B58" s="3"/>
       <c r="C58" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" s="2"/>
-      <c r="F58" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F58" s="2"/>
       <c r="G58" s="2"/>
       <c r="H58" s="2"/>
       <c r="I58" s="2"/>
@@ -3397,20 +4227,30 @@
       <c r="X58" s="5"/>
       <c r="Y58" s="5"/>
       <c r="Z58" s="5"/>
-    </row>
-    <row r="59" spans="1:26">
+      <c r="AA58" s="13"/>
+      <c r="AB58" s="13"/>
+      <c r="AC58" s="16"/>
+      <c r="AD58" s="16"/>
+      <c r="AE58" s="16"/>
+      <c r="AF58" s="17"/>
+      <c r="AG58" s="16"/>
+      <c r="AH58" s="17"/>
+      <c r="AI58" s="17"/>
+      <c r="AJ58" s="17"/>
+      <c r="AK58" s="14"/>
+      <c r="AL58" s="14"/>
+    </row>
+    <row r="59" spans="1:38">
       <c r="A59" s="2">
         <v>53</v>
       </c>
       <c r="B59" s="3"/>
       <c r="C59" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D59" s="2"/>
       <c r="E59" s="2"/>
-      <c r="F59" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F59" s="2"/>
       <c r="G59" s="2"/>
       <c r="H59" s="2"/>
       <c r="I59" s="2"/>
@@ -3434,20 +4274,30 @@
       <c r="X59" s="5"/>
       <c r="Y59" s="5"/>
       <c r="Z59" s="5"/>
-    </row>
-    <row r="60" spans="1:26">
+      <c r="AA59" s="13"/>
+      <c r="AB59" s="13"/>
+      <c r="AC59" s="16"/>
+      <c r="AD59" s="16"/>
+      <c r="AE59" s="16"/>
+      <c r="AF59" s="17"/>
+      <c r="AG59" s="16"/>
+      <c r="AH59" s="17"/>
+      <c r="AI59" s="17"/>
+      <c r="AJ59" s="17"/>
+      <c r="AK59" s="14"/>
+      <c r="AL59" s="14"/>
+    </row>
+    <row r="60" spans="1:38">
       <c r="A60" s="2">
         <v>54</v>
       </c>
       <c r="B60" s="3"/>
       <c r="C60" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D60" s="2"/>
       <c r="E60" s="2"/>
-      <c r="F60" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F60" s="2"/>
       <c r="G60" s="2"/>
       <c r="H60" s="2"/>
       <c r="I60" s="2"/>
@@ -3471,20 +4321,30 @@
       <c r="X60" s="5"/>
       <c r="Y60" s="5"/>
       <c r="Z60" s="5"/>
-    </row>
-    <row r="61" spans="1:26">
+      <c r="AA60" s="13"/>
+      <c r="AB60" s="13"/>
+      <c r="AC60" s="16"/>
+      <c r="AD60" s="16"/>
+      <c r="AE60" s="16"/>
+      <c r="AF60" s="17"/>
+      <c r="AG60" s="16"/>
+      <c r="AH60" s="17"/>
+      <c r="AI60" s="17"/>
+      <c r="AJ60" s="17"/>
+      <c r="AK60" s="14"/>
+      <c r="AL60" s="14"/>
+    </row>
+    <row r="61" spans="1:38">
       <c r="A61" s="2">
         <v>55</v>
       </c>
       <c r="B61" s="3"/>
       <c r="C61" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D61" s="2"/>
       <c r="E61" s="2"/>
-      <c r="F61" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F61" s="2"/>
       <c r="G61" s="2"/>
       <c r="H61" s="2"/>
       <c r="I61" s="2"/>
@@ -3508,20 +4368,30 @@
       <c r="X61" s="5"/>
       <c r="Y61" s="5"/>
       <c r="Z61" s="5"/>
-    </row>
-    <row r="62" spans="1:26">
+      <c r="AA61" s="13"/>
+      <c r="AB61" s="13"/>
+      <c r="AC61" s="16"/>
+      <c r="AD61" s="16"/>
+      <c r="AE61" s="16"/>
+      <c r="AF61" s="17"/>
+      <c r="AG61" s="16"/>
+      <c r="AH61" s="17"/>
+      <c r="AI61" s="17"/>
+      <c r="AJ61" s="17"/>
+      <c r="AK61" s="14"/>
+      <c r="AL61" s="14"/>
+    </row>
+    <row r="62" spans="1:38">
       <c r="A62" s="2">
         <v>56</v>
       </c>
       <c r="B62" s="3"/>
       <c r="C62" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D62" s="2"/>
       <c r="E62" s="2"/>
-      <c r="F62" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F62" s="2"/>
       <c r="G62" s="2"/>
       <c r="H62" s="2"/>
       <c r="I62" s="2"/>
@@ -3545,20 +4415,30 @@
       <c r="X62" s="5"/>
       <c r="Y62" s="5"/>
       <c r="Z62" s="5"/>
-    </row>
-    <row r="63" spans="1:26">
+      <c r="AA62" s="13"/>
+      <c r="AB62" s="13"/>
+      <c r="AC62" s="16"/>
+      <c r="AD62" s="16"/>
+      <c r="AE62" s="16"/>
+      <c r="AF62" s="17"/>
+      <c r="AG62" s="16"/>
+      <c r="AH62" s="17"/>
+      <c r="AI62" s="17"/>
+      <c r="AJ62" s="17"/>
+      <c r="AK62" s="14"/>
+      <c r="AL62" s="14"/>
+    </row>
+    <row r="63" spans="1:38">
       <c r="A63" s="2">
         <v>57</v>
       </c>
       <c r="B63" s="3"/>
       <c r="C63" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D63" s="2"/>
       <c r="E63" s="2"/>
-      <c r="F63" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F63" s="2"/>
       <c r="G63" s="2"/>
       <c r="H63" s="2"/>
       <c r="I63" s="2"/>
@@ -3582,20 +4462,30 @@
       <c r="X63" s="5"/>
       <c r="Y63" s="5"/>
       <c r="Z63" s="5"/>
-    </row>
-    <row r="64" spans="1:26">
+      <c r="AA63" s="13"/>
+      <c r="AB63" s="13"/>
+      <c r="AC63" s="16"/>
+      <c r="AD63" s="16"/>
+      <c r="AE63" s="16"/>
+      <c r="AF63" s="17"/>
+      <c r="AG63" s="16"/>
+      <c r="AH63" s="17"/>
+      <c r="AI63" s="17"/>
+      <c r="AJ63" s="17"/>
+      <c r="AK63" s="14"/>
+      <c r="AL63" s="14"/>
+    </row>
+    <row r="64" spans="1:38">
       <c r="A64" s="2">
         <v>58</v>
       </c>
       <c r="B64" s="3"/>
       <c r="C64" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D64" s="2"/>
       <c r="E64" s="2"/>
-      <c r="F64" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F64" s="2"/>
       <c r="G64" s="2"/>
       <c r="H64" s="2"/>
       <c r="I64" s="2"/>
@@ -3619,20 +4509,30 @@
       <c r="X64" s="5"/>
       <c r="Y64" s="5"/>
       <c r="Z64" s="5"/>
-    </row>
-    <row r="65" spans="1:26">
+      <c r="AA64" s="13"/>
+      <c r="AB64" s="13"/>
+      <c r="AC64" s="16"/>
+      <c r="AD64" s="16"/>
+      <c r="AE64" s="16"/>
+      <c r="AF64" s="17"/>
+      <c r="AG64" s="16"/>
+      <c r="AH64" s="17"/>
+      <c r="AI64" s="17"/>
+      <c r="AJ64" s="17"/>
+      <c r="AK64" s="14"/>
+      <c r="AL64" s="14"/>
+    </row>
+    <row r="65" spans="1:38">
       <c r="A65" s="2">
         <v>59</v>
       </c>
       <c r="B65" s="3"/>
       <c r="C65" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D65" s="2"/>
       <c r="E65" s="2"/>
-      <c r="F65" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F65" s="2"/>
       <c r="G65" s="2"/>
       <c r="H65" s="2"/>
       <c r="I65" s="2"/>
@@ -3656,20 +4556,30 @@
       <c r="X65" s="5"/>
       <c r="Y65" s="5"/>
       <c r="Z65" s="5"/>
-    </row>
-    <row r="66" spans="1:26">
+      <c r="AA65" s="13"/>
+      <c r="AB65" s="13"/>
+      <c r="AC65" s="16"/>
+      <c r="AD65" s="16"/>
+      <c r="AE65" s="16"/>
+      <c r="AF65" s="17"/>
+      <c r="AG65" s="16"/>
+      <c r="AH65" s="17"/>
+      <c r="AI65" s="17"/>
+      <c r="AJ65" s="17"/>
+      <c r="AK65" s="14"/>
+      <c r="AL65" s="14"/>
+    </row>
+    <row r="66" spans="1:38">
       <c r="A66" s="2">
         <v>60</v>
       </c>
       <c r="B66" s="3"/>
       <c r="C66" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D66" s="2"/>
       <c r="E66" s="2"/>
-      <c r="F66" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F66" s="2"/>
       <c r="G66" s="2"/>
       <c r="H66" s="2"/>
       <c r="I66" s="2"/>
@@ -3693,20 +4603,30 @@
       <c r="X66" s="5"/>
       <c r="Y66" s="5"/>
       <c r="Z66" s="5"/>
-    </row>
-    <row r="67" spans="1:26">
+      <c r="AA66" s="13"/>
+      <c r="AB66" s="13"/>
+      <c r="AC66" s="16"/>
+      <c r="AD66" s="16"/>
+      <c r="AE66" s="16"/>
+      <c r="AF66" s="17"/>
+      <c r="AG66" s="16"/>
+      <c r="AH66" s="17"/>
+      <c r="AI66" s="17"/>
+      <c r="AJ66" s="17"/>
+      <c r="AK66" s="14"/>
+      <c r="AL66" s="14"/>
+    </row>
+    <row r="67" spans="1:38">
       <c r="A67" s="2">
         <v>61</v>
       </c>
       <c r="B67" s="3"/>
       <c r="C67" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D67" s="2"/>
       <c r="E67" s="2"/>
-      <c r="F67" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F67" s="2"/>
       <c r="G67" s="2"/>
       <c r="H67" s="2"/>
       <c r="I67" s="2"/>
@@ -3730,20 +4650,30 @@
       <c r="X67" s="5"/>
       <c r="Y67" s="5"/>
       <c r="Z67" s="5"/>
-    </row>
-    <row r="68" spans="1:26">
+      <c r="AA67" s="13"/>
+      <c r="AB67" s="13"/>
+      <c r="AC67" s="16"/>
+      <c r="AD67" s="16"/>
+      <c r="AE67" s="16"/>
+      <c r="AF67" s="17"/>
+      <c r="AG67" s="16"/>
+      <c r="AH67" s="17"/>
+      <c r="AI67" s="17"/>
+      <c r="AJ67" s="17"/>
+      <c r="AK67" s="14"/>
+      <c r="AL67" s="14"/>
+    </row>
+    <row r="68" spans="1:38">
       <c r="A68" s="2">
         <v>62</v>
       </c>
       <c r="B68" s="3"/>
       <c r="C68" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D68" s="2"/>
       <c r="E68" s="2"/>
-      <c r="F68" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F68" s="2"/>
       <c r="G68" s="2"/>
       <c r="H68" s="2"/>
       <c r="I68" s="2"/>
@@ -3767,20 +4697,30 @@
       <c r="X68" s="5"/>
       <c r="Y68" s="5"/>
       <c r="Z68" s="5"/>
-    </row>
-    <row r="69" spans="1:26">
+      <c r="AA68" s="13"/>
+      <c r="AB68" s="13"/>
+      <c r="AC68" s="16"/>
+      <c r="AD68" s="16"/>
+      <c r="AE68" s="16"/>
+      <c r="AF68" s="17"/>
+      <c r="AG68" s="16"/>
+      <c r="AH68" s="17"/>
+      <c r="AI68" s="17"/>
+      <c r="AJ68" s="17"/>
+      <c r="AK68" s="14"/>
+      <c r="AL68" s="14"/>
+    </row>
+    <row r="69" spans="1:38">
       <c r="A69" s="2">
         <v>63</v>
       </c>
       <c r="B69" s="3"/>
       <c r="C69" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D69" s="2"/>
       <c r="E69" s="2"/>
-      <c r="F69" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F69" s="2"/>
       <c r="G69" s="2"/>
       <c r="H69" s="2"/>
       <c r="I69" s="2"/>
@@ -3804,20 +4744,30 @@
       <c r="X69" s="5"/>
       <c r="Y69" s="5"/>
       <c r="Z69" s="5"/>
-    </row>
-    <row r="70" spans="1:26">
+      <c r="AA69" s="13"/>
+      <c r="AB69" s="13"/>
+      <c r="AC69" s="16"/>
+      <c r="AD69" s="16"/>
+      <c r="AE69" s="16"/>
+      <c r="AF69" s="17"/>
+      <c r="AG69" s="16"/>
+      <c r="AH69" s="17"/>
+      <c r="AI69" s="17"/>
+      <c r="AJ69" s="17"/>
+      <c r="AK69" s="14"/>
+      <c r="AL69" s="14"/>
+    </row>
+    <row r="70" spans="1:38">
       <c r="A70" s="2">
         <v>64</v>
       </c>
       <c r="B70" s="3"/>
       <c r="C70" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D70" s="2"/>
       <c r="E70" s="2"/>
-      <c r="F70" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F70" s="2"/>
       <c r="G70" s="2"/>
       <c r="H70" s="2"/>
       <c r="I70" s="2"/>
@@ -3841,20 +4791,30 @@
       <c r="X70" s="5"/>
       <c r="Y70" s="5"/>
       <c r="Z70" s="5"/>
-    </row>
-    <row r="71" spans="1:26">
+      <c r="AA70" s="13"/>
+      <c r="AB70" s="13"/>
+      <c r="AC70" s="16"/>
+      <c r="AD70" s="16"/>
+      <c r="AE70" s="16"/>
+      <c r="AF70" s="17"/>
+      <c r="AG70" s="16"/>
+      <c r="AH70" s="17"/>
+      <c r="AI70" s="17"/>
+      <c r="AJ70" s="17"/>
+      <c r="AK70" s="14"/>
+      <c r="AL70" s="14"/>
+    </row>
+    <row r="71" spans="1:38">
       <c r="A71" s="2">
         <v>65</v>
       </c>
       <c r="B71" s="3"/>
       <c r="C71" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D71" s="2"/>
       <c r="E71" s="2"/>
-      <c r="F71" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F71" s="2"/>
       <c r="G71" s="2"/>
       <c r="H71" s="2"/>
       <c r="I71" s="2"/>
@@ -3878,20 +4838,30 @@
       <c r="X71" s="5"/>
       <c r="Y71" s="5"/>
       <c r="Z71" s="5"/>
-    </row>
-    <row r="72" spans="1:26">
+      <c r="AA71" s="13"/>
+      <c r="AB71" s="13"/>
+      <c r="AC71" s="16"/>
+      <c r="AD71" s="16"/>
+      <c r="AE71" s="16"/>
+      <c r="AF71" s="17"/>
+      <c r="AG71" s="16"/>
+      <c r="AH71" s="17"/>
+      <c r="AI71" s="17"/>
+      <c r="AJ71" s="17"/>
+      <c r="AK71" s="14"/>
+      <c r="AL71" s="14"/>
+    </row>
+    <row r="72" spans="1:38">
       <c r="A72" s="2">
         <v>66</v>
       </c>
       <c r="B72" s="3"/>
       <c r="C72" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D72" s="2"/>
       <c r="E72" s="2"/>
-      <c r="F72" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F72" s="2"/>
       <c r="G72" s="2"/>
       <c r="H72" s="2"/>
       <c r="I72" s="2"/>
@@ -3915,20 +4885,30 @@
       <c r="X72" s="5"/>
       <c r="Y72" s="5"/>
       <c r="Z72" s="5"/>
-    </row>
-    <row r="73" spans="1:26">
+      <c r="AA72" s="13"/>
+      <c r="AB72" s="13"/>
+      <c r="AC72" s="16"/>
+      <c r="AD72" s="16"/>
+      <c r="AE72" s="16"/>
+      <c r="AF72" s="17"/>
+      <c r="AG72" s="16"/>
+      <c r="AH72" s="17"/>
+      <c r="AI72" s="17"/>
+      <c r="AJ72" s="17"/>
+      <c r="AK72" s="14"/>
+      <c r="AL72" s="14"/>
+    </row>
+    <row r="73" spans="1:38">
       <c r="A73" s="2">
         <v>67</v>
       </c>
       <c r="B73" s="3"/>
       <c r="C73" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D73" s="2"/>
       <c r="E73" s="2"/>
-      <c r="F73" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F73" s="2"/>
       <c r="G73" s="2"/>
       <c r="H73" s="2"/>
       <c r="I73" s="2"/>
@@ -3952,20 +4932,30 @@
       <c r="X73" s="5"/>
       <c r="Y73" s="5"/>
       <c r="Z73" s="5"/>
-    </row>
-    <row r="74" spans="1:26">
+      <c r="AA73" s="13"/>
+      <c r="AB73" s="13"/>
+      <c r="AC73" s="16"/>
+      <c r="AD73" s="16"/>
+      <c r="AE73" s="16"/>
+      <c r="AF73" s="17"/>
+      <c r="AG73" s="16"/>
+      <c r="AH73" s="17"/>
+      <c r="AI73" s="17"/>
+      <c r="AJ73" s="17"/>
+      <c r="AK73" s="14"/>
+      <c r="AL73" s="14"/>
+    </row>
+    <row r="74" spans="1:38">
       <c r="A74" s="2">
         <v>68</v>
       </c>
       <c r="B74" s="3"/>
       <c r="C74" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D74" s="2"/>
       <c r="E74" s="2"/>
-      <c r="F74" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F74" s="2"/>
       <c r="G74" s="2"/>
       <c r="H74" s="2"/>
       <c r="I74" s="2"/>
@@ -3989,20 +4979,30 @@
       <c r="X74" s="5"/>
       <c r="Y74" s="5"/>
       <c r="Z74" s="5"/>
-    </row>
-    <row r="75" spans="1:26">
+      <c r="AA74" s="13"/>
+      <c r="AB74" s="13"/>
+      <c r="AC74" s="16"/>
+      <c r="AD74" s="16"/>
+      <c r="AE74" s="16"/>
+      <c r="AF74" s="17"/>
+      <c r="AG74" s="16"/>
+      <c r="AH74" s="17"/>
+      <c r="AI74" s="17"/>
+      <c r="AJ74" s="17"/>
+      <c r="AK74" s="14"/>
+      <c r="AL74" s="14"/>
+    </row>
+    <row r="75" spans="1:38">
       <c r="A75" s="2">
         <v>69</v>
       </c>
       <c r="B75" s="3"/>
       <c r="C75" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D75" s="2"/>
       <c r="E75" s="2"/>
-      <c r="F75" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F75" s="2"/>
       <c r="G75" s="2"/>
       <c r="H75" s="2"/>
       <c r="I75" s="2"/>
@@ -4026,20 +5026,30 @@
       <c r="X75" s="5"/>
       <c r="Y75" s="5"/>
       <c r="Z75" s="5"/>
-    </row>
-    <row r="76" spans="1:26">
+      <c r="AA75" s="13"/>
+      <c r="AB75" s="13"/>
+      <c r="AC75" s="16"/>
+      <c r="AD75" s="16"/>
+      <c r="AE75" s="16"/>
+      <c r="AF75" s="17"/>
+      <c r="AG75" s="16"/>
+      <c r="AH75" s="17"/>
+      <c r="AI75" s="17"/>
+      <c r="AJ75" s="17"/>
+      <c r="AK75" s="14"/>
+      <c r="AL75" s="14"/>
+    </row>
+    <row r="76" spans="1:38">
       <c r="A76" s="2">
         <v>70</v>
       </c>
       <c r="B76" s="3"/>
       <c r="C76" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D76" s="2"/>
       <c r="E76" s="2"/>
-      <c r="F76" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F76" s="2"/>
       <c r="G76" s="2"/>
       <c r="H76" s="2"/>
       <c r="I76" s="2"/>
@@ -4063,20 +5073,30 @@
       <c r="X76" s="5"/>
       <c r="Y76" s="5"/>
       <c r="Z76" s="5"/>
-    </row>
-    <row r="77" spans="1:26">
+      <c r="AA76" s="13"/>
+      <c r="AB76" s="13"/>
+      <c r="AC76" s="16"/>
+      <c r="AD76" s="16"/>
+      <c r="AE76" s="16"/>
+      <c r="AF76" s="17"/>
+      <c r="AG76" s="16"/>
+      <c r="AH76" s="17"/>
+      <c r="AI76" s="17"/>
+      <c r="AJ76" s="17"/>
+      <c r="AK76" s="14"/>
+      <c r="AL76" s="14"/>
+    </row>
+    <row r="77" spans="1:38">
       <c r="A77" s="2">
         <v>71</v>
       </c>
       <c r="B77" s="3"/>
       <c r="C77" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D77" s="2"/>
       <c r="E77" s="2"/>
-      <c r="F77" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F77" s="2"/>
       <c r="G77" s="2"/>
       <c r="H77" s="2"/>
       <c r="I77" s="2"/>
@@ -4100,20 +5120,30 @@
       <c r="X77" s="5"/>
       <c r="Y77" s="5"/>
       <c r="Z77" s="5"/>
-    </row>
-    <row r="78" spans="1:26">
+      <c r="AA77" s="13"/>
+      <c r="AB77" s="13"/>
+      <c r="AC77" s="16"/>
+      <c r="AD77" s="16"/>
+      <c r="AE77" s="16"/>
+      <c r="AF77" s="17"/>
+      <c r="AG77" s="16"/>
+      <c r="AH77" s="17"/>
+      <c r="AI77" s="17"/>
+      <c r="AJ77" s="17"/>
+      <c r="AK77" s="14"/>
+      <c r="AL77" s="14"/>
+    </row>
+    <row r="78" spans="1:38">
       <c r="A78" s="2">
         <v>72</v>
       </c>
       <c r="B78" s="3"/>
       <c r="C78" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D78" s="2"/>
       <c r="E78" s="2"/>
-      <c r="F78" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F78" s="2"/>
       <c r="G78" s="2"/>
       <c r="H78" s="2"/>
       <c r="I78" s="2"/>
@@ -4137,20 +5167,30 @@
       <c r="X78" s="5"/>
       <c r="Y78" s="5"/>
       <c r="Z78" s="5"/>
-    </row>
-    <row r="79" spans="1:26">
+      <c r="AA78" s="13"/>
+      <c r="AB78" s="13"/>
+      <c r="AC78" s="16"/>
+      <c r="AD78" s="16"/>
+      <c r="AE78" s="16"/>
+      <c r="AF78" s="17"/>
+      <c r="AG78" s="16"/>
+      <c r="AH78" s="17"/>
+      <c r="AI78" s="17"/>
+      <c r="AJ78" s="17"/>
+      <c r="AK78" s="14"/>
+      <c r="AL78" s="14"/>
+    </row>
+    <row r="79" spans="1:38">
       <c r="A79" s="2">
         <v>73</v>
       </c>
       <c r="B79" s="3"/>
       <c r="C79" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D79" s="2"/>
       <c r="E79" s="2"/>
-      <c r="F79" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F79" s="2"/>
       <c r="G79" s="2"/>
       <c r="H79" s="2"/>
       <c r="I79" s="2"/>
@@ -4174,20 +5214,30 @@
       <c r="X79" s="5"/>
       <c r="Y79" s="5"/>
       <c r="Z79" s="5"/>
-    </row>
-    <row r="80" spans="1:26">
+      <c r="AA79" s="13"/>
+      <c r="AB79" s="13"/>
+      <c r="AC79" s="16"/>
+      <c r="AD79" s="16"/>
+      <c r="AE79" s="16"/>
+      <c r="AF79" s="17"/>
+      <c r="AG79" s="16"/>
+      <c r="AH79" s="17"/>
+      <c r="AI79" s="17"/>
+      <c r="AJ79" s="17"/>
+      <c r="AK79" s="14"/>
+      <c r="AL79" s="14"/>
+    </row>
+    <row r="80" spans="1:38">
       <c r="A80" s="2">
         <v>74</v>
       </c>
       <c r="B80" s="3"/>
       <c r="C80" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D80" s="2"/>
       <c r="E80" s="2"/>
-      <c r="F80" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F80" s="2"/>
       <c r="G80" s="2"/>
       <c r="H80" s="2"/>
       <c r="I80" s="2"/>
@@ -4211,20 +5261,30 @@
       <c r="X80" s="5"/>
       <c r="Y80" s="5"/>
       <c r="Z80" s="5"/>
-    </row>
-    <row r="81" spans="1:26">
+      <c r="AA80" s="13"/>
+      <c r="AB80" s="13"/>
+      <c r="AC80" s="16"/>
+      <c r="AD80" s="16"/>
+      <c r="AE80" s="16"/>
+      <c r="AF80" s="17"/>
+      <c r="AG80" s="16"/>
+      <c r="AH80" s="17"/>
+      <c r="AI80" s="17"/>
+      <c r="AJ80" s="17"/>
+      <c r="AK80" s="14"/>
+      <c r="AL80" s="14"/>
+    </row>
+    <row r="81" spans="1:38">
       <c r="A81" s="2">
         <v>75</v>
       </c>
       <c r="B81" s="3"/>
       <c r="C81" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D81" s="2"/>
       <c r="E81" s="2"/>
-      <c r="F81" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F81" s="2"/>
       <c r="G81" s="2"/>
       <c r="H81" s="2"/>
       <c r="I81" s="2"/>
@@ -4248,20 +5308,30 @@
       <c r="X81" s="5"/>
       <c r="Y81" s="5"/>
       <c r="Z81" s="5"/>
-    </row>
-    <row r="82" spans="1:26">
+      <c r="AA81" s="13"/>
+      <c r="AB81" s="13"/>
+      <c r="AC81" s="16"/>
+      <c r="AD81" s="16"/>
+      <c r="AE81" s="16"/>
+      <c r="AF81" s="17"/>
+      <c r="AG81" s="16"/>
+      <c r="AH81" s="17"/>
+      <c r="AI81" s="17"/>
+      <c r="AJ81" s="17"/>
+      <c r="AK81" s="14"/>
+      <c r="AL81" s="14"/>
+    </row>
+    <row r="82" spans="1:38">
       <c r="A82" s="2">
         <v>76</v>
       </c>
       <c r="B82" s="3"/>
       <c r="C82" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D82" s="2"/>
       <c r="E82" s="2"/>
-      <c r="F82" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F82" s="2"/>
       <c r="G82" s="2"/>
       <c r="H82" s="2"/>
       <c r="I82" s="2"/>
@@ -4285,20 +5355,30 @@
       <c r="X82" s="5"/>
       <c r="Y82" s="5"/>
       <c r="Z82" s="5"/>
-    </row>
-    <row r="83" spans="1:26">
+      <c r="AA82" s="13"/>
+      <c r="AB82" s="13"/>
+      <c r="AC82" s="16"/>
+      <c r="AD82" s="16"/>
+      <c r="AE82" s="16"/>
+      <c r="AF82" s="17"/>
+      <c r="AG82" s="16"/>
+      <c r="AH82" s="17"/>
+      <c r="AI82" s="17"/>
+      <c r="AJ82" s="17"/>
+      <c r="AK82" s="14"/>
+      <c r="AL82" s="14"/>
+    </row>
+    <row r="83" spans="1:38">
       <c r="A83" s="2">
         <v>77</v>
       </c>
       <c r="B83" s="3"/>
       <c r="C83" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D83" s="2"/>
       <c r="E83" s="2"/>
-      <c r="F83" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F83" s="2"/>
       <c r="G83" s="2"/>
       <c r="H83" s="2"/>
       <c r="I83" s="2"/>
@@ -4322,20 +5402,30 @@
       <c r="X83" s="5"/>
       <c r="Y83" s="5"/>
       <c r="Z83" s="5"/>
-    </row>
-    <row r="84" spans="1:26">
+      <c r="AA83" s="13"/>
+      <c r="AB83" s="13"/>
+      <c r="AC83" s="16"/>
+      <c r="AD83" s="16"/>
+      <c r="AE83" s="16"/>
+      <c r="AF83" s="17"/>
+      <c r="AG83" s="16"/>
+      <c r="AH83" s="17"/>
+      <c r="AI83" s="17"/>
+      <c r="AJ83" s="17"/>
+      <c r="AK83" s="14"/>
+      <c r="AL83" s="14"/>
+    </row>
+    <row r="84" spans="1:38">
       <c r="A84" s="2">
         <v>78</v>
       </c>
       <c r="B84" s="3"/>
       <c r="C84" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D84" s="2"/>
       <c r="E84" s="2"/>
-      <c r="F84" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F84" s="2"/>
       <c r="G84" s="2"/>
       <c r="H84" s="2"/>
       <c r="I84" s="2"/>
@@ -4359,20 +5449,30 @@
       <c r="X84" s="5"/>
       <c r="Y84" s="5"/>
       <c r="Z84" s="5"/>
-    </row>
-    <row r="85" spans="1:26">
+      <c r="AA84" s="13"/>
+      <c r="AB84" s="13"/>
+      <c r="AC84" s="16"/>
+      <c r="AD84" s="16"/>
+      <c r="AE84" s="16"/>
+      <c r="AF84" s="17"/>
+      <c r="AG84" s="16"/>
+      <c r="AH84" s="17"/>
+      <c r="AI84" s="17"/>
+      <c r="AJ84" s="17"/>
+      <c r="AK84" s="14"/>
+      <c r="AL84" s="14"/>
+    </row>
+    <row r="85" spans="1:38">
       <c r="A85" s="2">
         <v>79</v>
       </c>
       <c r="B85" s="3"/>
       <c r="C85" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D85" s="2"/>
       <c r="E85" s="2"/>
-      <c r="F85" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F85" s="2"/>
       <c r="G85" s="2"/>
       <c r="H85" s="2"/>
       <c r="I85" s="2"/>
@@ -4396,20 +5496,30 @@
       <c r="X85" s="5"/>
       <c r="Y85" s="5"/>
       <c r="Z85" s="5"/>
-    </row>
-    <row r="86" spans="1:26">
+      <c r="AA85" s="13"/>
+      <c r="AB85" s="13"/>
+      <c r="AC85" s="16"/>
+      <c r="AD85" s="16"/>
+      <c r="AE85" s="16"/>
+      <c r="AF85" s="17"/>
+      <c r="AG85" s="16"/>
+      <c r="AH85" s="17"/>
+      <c r="AI85" s="17"/>
+      <c r="AJ85" s="17"/>
+      <c r="AK85" s="14"/>
+      <c r="AL85" s="14"/>
+    </row>
+    <row r="86" spans="1:38">
       <c r="A86" s="2">
         <v>80</v>
       </c>
       <c r="B86" s="3"/>
       <c r="C86" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D86" s="2"/>
       <c r="E86" s="2"/>
-      <c r="F86" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F86" s="2"/>
       <c r="G86" s="2"/>
       <c r="H86" s="2"/>
       <c r="I86" s="2"/>
@@ -4433,20 +5543,30 @@
       <c r="X86" s="5"/>
       <c r="Y86" s="5"/>
       <c r="Z86" s="5"/>
-    </row>
-    <row r="87" spans="1:26">
+      <c r="AA86" s="13"/>
+      <c r="AB86" s="13"/>
+      <c r="AC86" s="16"/>
+      <c r="AD86" s="16"/>
+      <c r="AE86" s="16"/>
+      <c r="AF86" s="17"/>
+      <c r="AG86" s="16"/>
+      <c r="AH86" s="17"/>
+      <c r="AI86" s="17"/>
+      <c r="AJ86" s="17"/>
+      <c r="AK86" s="14"/>
+      <c r="AL86" s="14"/>
+    </row>
+    <row r="87" spans="1:38">
       <c r="A87" s="2">
         <v>81</v>
       </c>
       <c r="B87" s="3"/>
       <c r="C87" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D87" s="2"/>
       <c r="E87" s="2"/>
-      <c r="F87" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F87" s="2"/>
       <c r="G87" s="2"/>
       <c r="H87" s="2"/>
       <c r="I87" s="2"/>
@@ -4470,20 +5590,30 @@
       <c r="X87" s="5"/>
       <c r="Y87" s="5"/>
       <c r="Z87" s="5"/>
-    </row>
-    <row r="88" spans="1:26">
+      <c r="AA87" s="13"/>
+      <c r="AB87" s="13"/>
+      <c r="AC87" s="16"/>
+      <c r="AD87" s="16"/>
+      <c r="AE87" s="16"/>
+      <c r="AF87" s="17"/>
+      <c r="AG87" s="16"/>
+      <c r="AH87" s="17"/>
+      <c r="AI87" s="17"/>
+      <c r="AJ87" s="17"/>
+      <c r="AK87" s="14"/>
+      <c r="AL87" s="14"/>
+    </row>
+    <row r="88" spans="1:38">
       <c r="A88" s="2">
         <v>82</v>
       </c>
       <c r="B88" s="3"/>
       <c r="C88" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D88" s="2"/>
       <c r="E88" s="2"/>
-      <c r="F88" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F88" s="2"/>
       <c r="G88" s="2"/>
       <c r="H88" s="2"/>
       <c r="I88" s="2"/>
@@ -4507,20 +5637,30 @@
       <c r="X88" s="5"/>
       <c r="Y88" s="5"/>
       <c r="Z88" s="5"/>
-    </row>
-    <row r="89" spans="1:26">
+      <c r="AA88" s="13"/>
+      <c r="AB88" s="13"/>
+      <c r="AC88" s="16"/>
+      <c r="AD88" s="16"/>
+      <c r="AE88" s="16"/>
+      <c r="AF88" s="17"/>
+      <c r="AG88" s="16"/>
+      <c r="AH88" s="17"/>
+      <c r="AI88" s="17"/>
+      <c r="AJ88" s="17"/>
+      <c r="AK88" s="14"/>
+      <c r="AL88" s="14"/>
+    </row>
+    <row r="89" spans="1:38">
       <c r="A89" s="2">
         <v>83</v>
       </c>
       <c r="B89" s="3"/>
       <c r="C89" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D89" s="2"/>
       <c r="E89" s="2"/>
-      <c r="F89" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F89" s="2"/>
       <c r="G89" s="2"/>
       <c r="H89" s="2"/>
       <c r="I89" s="2"/>
@@ -4544,20 +5684,30 @@
       <c r="X89" s="5"/>
       <c r="Y89" s="5"/>
       <c r="Z89" s="5"/>
-    </row>
-    <row r="90" spans="1:26">
+      <c r="AA89" s="13"/>
+      <c r="AB89" s="13"/>
+      <c r="AC89" s="16"/>
+      <c r="AD89" s="16"/>
+      <c r="AE89" s="16"/>
+      <c r="AF89" s="17"/>
+      <c r="AG89" s="16"/>
+      <c r="AH89" s="17"/>
+      <c r="AI89" s="17"/>
+      <c r="AJ89" s="17"/>
+      <c r="AK89" s="14"/>
+      <c r="AL89" s="14"/>
+    </row>
+    <row r="90" spans="1:38">
       <c r="A90" s="2">
         <v>84</v>
       </c>
       <c r="B90" s="3"/>
       <c r="C90" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D90" s="2"/>
       <c r="E90" s="2"/>
-      <c r="F90" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F90" s="2"/>
       <c r="G90" s="2"/>
       <c r="H90" s="2"/>
       <c r="I90" s="2"/>
@@ -4581,20 +5731,30 @@
       <c r="X90" s="5"/>
       <c r="Y90" s="5"/>
       <c r="Z90" s="5"/>
-    </row>
-    <row r="91" spans="1:26">
+      <c r="AA90" s="13"/>
+      <c r="AB90" s="13"/>
+      <c r="AC90" s="16"/>
+      <c r="AD90" s="16"/>
+      <c r="AE90" s="16"/>
+      <c r="AF90" s="17"/>
+      <c r="AG90" s="16"/>
+      <c r="AH90" s="17"/>
+      <c r="AI90" s="17"/>
+      <c r="AJ90" s="17"/>
+      <c r="AK90" s="14"/>
+      <c r="AL90" s="14"/>
+    </row>
+    <row r="91" spans="1:38">
       <c r="A91" s="2">
         <v>85</v>
       </c>
       <c r="B91" s="3"/>
       <c r="C91" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D91" s="2"/>
       <c r="E91" s="2"/>
-      <c r="F91" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F91" s="2"/>
       <c r="G91" s="2"/>
       <c r="H91" s="2"/>
       <c r="I91" s="2"/>
@@ -4618,20 +5778,30 @@
       <c r="X91" s="5"/>
       <c r="Y91" s="5"/>
       <c r="Z91" s="5"/>
-    </row>
-    <row r="92" spans="1:26">
+      <c r="AA91" s="13"/>
+      <c r="AB91" s="13"/>
+      <c r="AC91" s="16"/>
+      <c r="AD91" s="16"/>
+      <c r="AE91" s="16"/>
+      <c r="AF91" s="17"/>
+      <c r="AG91" s="16"/>
+      <c r="AH91" s="17"/>
+      <c r="AI91" s="17"/>
+      <c r="AJ91" s="17"/>
+      <c r="AK91" s="14"/>
+      <c r="AL91" s="14"/>
+    </row>
+    <row r="92" spans="1:38">
       <c r="A92" s="2">
         <v>86</v>
       </c>
       <c r="B92" s="3"/>
       <c r="C92" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D92" s="2"/>
       <c r="E92" s="2"/>
-      <c r="F92" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F92" s="2"/>
       <c r="G92" s="2"/>
       <c r="H92" s="2"/>
       <c r="I92" s="2"/>
@@ -4655,20 +5825,30 @@
       <c r="X92" s="5"/>
       <c r="Y92" s="5"/>
       <c r="Z92" s="5"/>
-    </row>
-    <row r="93" spans="1:26">
+      <c r="AA92" s="13"/>
+      <c r="AB92" s="13"/>
+      <c r="AC92" s="16"/>
+      <c r="AD92" s="16"/>
+      <c r="AE92" s="16"/>
+      <c r="AF92" s="17"/>
+      <c r="AG92" s="16"/>
+      <c r="AH92" s="17"/>
+      <c r="AI92" s="17"/>
+      <c r="AJ92" s="17"/>
+      <c r="AK92" s="14"/>
+      <c r="AL92" s="14"/>
+    </row>
+    <row r="93" spans="1:38">
       <c r="A93" s="2">
         <v>87</v>
       </c>
       <c r="B93" s="3"/>
       <c r="C93" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D93" s="2"/>
       <c r="E93" s="2"/>
-      <c r="F93" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F93" s="2"/>
       <c r="G93" s="2"/>
       <c r="H93" s="2"/>
       <c r="I93" s="2"/>
@@ -4692,20 +5872,30 @@
       <c r="X93" s="5"/>
       <c r="Y93" s="5"/>
       <c r="Z93" s="5"/>
-    </row>
-    <row r="94" spans="1:26">
+      <c r="AA93" s="13"/>
+      <c r="AB93" s="13"/>
+      <c r="AC93" s="16"/>
+      <c r="AD93" s="16"/>
+      <c r="AE93" s="16"/>
+      <c r="AF93" s="17"/>
+      <c r="AG93" s="16"/>
+      <c r="AH93" s="17"/>
+      <c r="AI93" s="17"/>
+      <c r="AJ93" s="17"/>
+      <c r="AK93" s="14"/>
+      <c r="AL93" s="14"/>
+    </row>
+    <row r="94" spans="1:38">
       <c r="A94" s="2">
         <v>88</v>
       </c>
       <c r="B94" s="3"/>
       <c r="C94" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D94" s="2"/>
       <c r="E94" s="2"/>
-      <c r="F94" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F94" s="2"/>
       <c r="G94" s="2"/>
       <c r="H94" s="2"/>
       <c r="I94" s="2"/>
@@ -4729,20 +5919,30 @@
       <c r="X94" s="5"/>
       <c r="Y94" s="5"/>
       <c r="Z94" s="5"/>
-    </row>
-    <row r="95" spans="1:26">
+      <c r="AA94" s="13"/>
+      <c r="AB94" s="13"/>
+      <c r="AC94" s="16"/>
+      <c r="AD94" s="16"/>
+      <c r="AE94" s="16"/>
+      <c r="AF94" s="17"/>
+      <c r="AG94" s="16"/>
+      <c r="AH94" s="17"/>
+      <c r="AI94" s="17"/>
+      <c r="AJ94" s="17"/>
+      <c r="AK94" s="14"/>
+      <c r="AL94" s="14"/>
+    </row>
+    <row r="95" spans="1:38">
       <c r="A95" s="2">
         <v>89</v>
       </c>
       <c r="B95" s="3"/>
       <c r="C95" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D95" s="2"/>
       <c r="E95" s="2"/>
-      <c r="F95" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F95" s="2"/>
       <c r="G95" s="2"/>
       <c r="H95" s="2"/>
       <c r="I95" s="2"/>
@@ -4766,20 +5966,30 @@
       <c r="X95" s="5"/>
       <c r="Y95" s="5"/>
       <c r="Z95" s="5"/>
-    </row>
-    <row r="96" spans="1:26">
+      <c r="AA95" s="13"/>
+      <c r="AB95" s="13"/>
+      <c r="AC95" s="16"/>
+      <c r="AD95" s="16"/>
+      <c r="AE95" s="16"/>
+      <c r="AF95" s="17"/>
+      <c r="AG95" s="16"/>
+      <c r="AH95" s="17"/>
+      <c r="AI95" s="17"/>
+      <c r="AJ95" s="17"/>
+      <c r="AK95" s="14"/>
+      <c r="AL95" s="14"/>
+    </row>
+    <row r="96" spans="1:38">
       <c r="A96" s="2">
         <v>90</v>
       </c>
       <c r="B96" s="3"/>
       <c r="C96" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D96" s="2"/>
       <c r="E96" s="2"/>
-      <c r="F96" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F96" s="2"/>
       <c r="G96" s="2"/>
       <c r="H96" s="2"/>
       <c r="I96" s="2"/>
@@ -4803,20 +6013,30 @@
       <c r="X96" s="5"/>
       <c r="Y96" s="5"/>
       <c r="Z96" s="5"/>
-    </row>
-    <row r="97" spans="1:26">
+      <c r="AA96" s="13"/>
+      <c r="AB96" s="13"/>
+      <c r="AC96" s="16"/>
+      <c r="AD96" s="16"/>
+      <c r="AE96" s="16"/>
+      <c r="AF96" s="17"/>
+      <c r="AG96" s="16"/>
+      <c r="AH96" s="17"/>
+      <c r="AI96" s="17"/>
+      <c r="AJ96" s="17"/>
+      <c r="AK96" s="14"/>
+      <c r="AL96" s="14"/>
+    </row>
+    <row r="97" spans="1:38">
       <c r="A97" s="2">
         <v>91</v>
       </c>
       <c r="B97" s="3"/>
       <c r="C97" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D97" s="2"/>
       <c r="E97" s="2"/>
-      <c r="F97" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F97" s="2"/>
       <c r="G97" s="2"/>
       <c r="H97" s="2"/>
       <c r="I97" s="2"/>
@@ -4840,20 +6060,30 @@
       <c r="X97" s="5"/>
       <c r="Y97" s="5"/>
       <c r="Z97" s="5"/>
-    </row>
-    <row r="98" spans="1:26">
+      <c r="AA97" s="13"/>
+      <c r="AB97" s="13"/>
+      <c r="AC97" s="16"/>
+      <c r="AD97" s="16"/>
+      <c r="AE97" s="16"/>
+      <c r="AF97" s="17"/>
+      <c r="AG97" s="16"/>
+      <c r="AH97" s="17"/>
+      <c r="AI97" s="17"/>
+      <c r="AJ97" s="17"/>
+      <c r="AK97" s="14"/>
+      <c r="AL97" s="14"/>
+    </row>
+    <row r="98" spans="1:38">
       <c r="A98" s="2">
         <v>92</v>
       </c>
       <c r="B98" s="3"/>
       <c r="C98" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D98" s="2"/>
       <c r="E98" s="2"/>
-      <c r="F98" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F98" s="2"/>
       <c r="G98" s="2"/>
       <c r="H98" s="2"/>
       <c r="I98" s="2"/>
@@ -4877,20 +6107,30 @@
       <c r="X98" s="5"/>
       <c r="Y98" s="5"/>
       <c r="Z98" s="5"/>
-    </row>
-    <row r="99" spans="1:26">
+      <c r="AA98" s="13"/>
+      <c r="AB98" s="13"/>
+      <c r="AC98" s="16"/>
+      <c r="AD98" s="16"/>
+      <c r="AE98" s="16"/>
+      <c r="AF98" s="17"/>
+      <c r="AG98" s="16"/>
+      <c r="AH98" s="17"/>
+      <c r="AI98" s="17"/>
+      <c r="AJ98" s="17"/>
+      <c r="AK98" s="14"/>
+      <c r="AL98" s="14"/>
+    </row>
+    <row r="99" spans="1:38">
       <c r="A99" s="2">
         <v>93</v>
       </c>
       <c r="B99" s="3"/>
       <c r="C99" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D99" s="2"/>
       <c r="E99" s="2"/>
-      <c r="F99" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F99" s="2"/>
       <c r="G99" s="2"/>
       <c r="H99" s="2"/>
       <c r="I99" s="2"/>
@@ -4914,20 +6154,30 @@
       <c r="X99" s="5"/>
       <c r="Y99" s="5"/>
       <c r="Z99" s="5"/>
-    </row>
-    <row r="100" spans="1:26">
+      <c r="AA99" s="13"/>
+      <c r="AB99" s="13"/>
+      <c r="AC99" s="16"/>
+      <c r="AD99" s="16"/>
+      <c r="AE99" s="16"/>
+      <c r="AF99" s="17"/>
+      <c r="AG99" s="16"/>
+      <c r="AH99" s="17"/>
+      <c r="AI99" s="17"/>
+      <c r="AJ99" s="17"/>
+      <c r="AK99" s="14"/>
+      <c r="AL99" s="14"/>
+    </row>
+    <row r="100" spans="1:38">
       <c r="A100" s="2">
         <v>94</v>
       </c>
       <c r="B100" s="3"/>
       <c r="C100" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D100" s="2"/>
       <c r="E100" s="2"/>
-      <c r="F100" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F100" s="2"/>
       <c r="G100" s="2"/>
       <c r="H100" s="2"/>
       <c r="I100" s="2"/>
@@ -4951,20 +6201,30 @@
       <c r="X100" s="5"/>
       <c r="Y100" s="5"/>
       <c r="Z100" s="5"/>
-    </row>
-    <row r="101" spans="1:26">
+      <c r="AA100" s="13"/>
+      <c r="AB100" s="13"/>
+      <c r="AC100" s="16"/>
+      <c r="AD100" s="16"/>
+      <c r="AE100" s="16"/>
+      <c r="AF100" s="17"/>
+      <c r="AG100" s="16"/>
+      <c r="AH100" s="17"/>
+      <c r="AI100" s="17"/>
+      <c r="AJ100" s="17"/>
+      <c r="AK100" s="14"/>
+      <c r="AL100" s="14"/>
+    </row>
+    <row r="101" spans="1:38">
       <c r="A101" s="2">
         <v>95</v>
       </c>
       <c r="B101" s="3"/>
       <c r="C101" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D101" s="2"/>
       <c r="E101" s="2"/>
-      <c r="F101" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F101" s="2"/>
       <c r="G101" s="2"/>
       <c r="H101" s="2"/>
       <c r="I101" s="2"/>
@@ -4988,20 +6248,30 @@
       <c r="X101" s="5"/>
       <c r="Y101" s="5"/>
       <c r="Z101" s="5"/>
-    </row>
-    <row r="102" spans="1:26">
+      <c r="AA101" s="13"/>
+      <c r="AB101" s="13"/>
+      <c r="AC101" s="16"/>
+      <c r="AD101" s="16"/>
+      <c r="AE101" s="16"/>
+      <c r="AF101" s="17"/>
+      <c r="AG101" s="16"/>
+      <c r="AH101" s="17"/>
+      <c r="AI101" s="17"/>
+      <c r="AJ101" s="17"/>
+      <c r="AK101" s="14"/>
+      <c r="AL101" s="14"/>
+    </row>
+    <row r="102" spans="1:38">
       <c r="A102" s="2">
         <v>96</v>
       </c>
       <c r="B102" s="3"/>
       <c r="C102" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D102" s="2"/>
       <c r="E102" s="2"/>
-      <c r="F102" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F102" s="2"/>
       <c r="G102" s="2"/>
       <c r="H102" s="2"/>
       <c r="I102" s="2"/>
@@ -5025,20 +6295,30 @@
       <c r="X102" s="5"/>
       <c r="Y102" s="5"/>
       <c r="Z102" s="5"/>
-    </row>
-    <row r="103" spans="1:26">
+      <c r="AA102" s="13"/>
+      <c r="AB102" s="13"/>
+      <c r="AC102" s="16"/>
+      <c r="AD102" s="16"/>
+      <c r="AE102" s="16"/>
+      <c r="AF102" s="17"/>
+      <c r="AG102" s="16"/>
+      <c r="AH102" s="17"/>
+      <c r="AI102" s="17"/>
+      <c r="AJ102" s="17"/>
+      <c r="AK102" s="14"/>
+      <c r="AL102" s="14"/>
+    </row>
+    <row r="103" spans="1:38">
       <c r="A103" s="2">
         <v>97</v>
       </c>
       <c r="B103" s="3"/>
       <c r="C103" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D103" s="2"/>
       <c r="E103" s="2"/>
-      <c r="F103" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F103" s="2"/>
       <c r="G103" s="2"/>
       <c r="H103" s="2"/>
       <c r="I103" s="2"/>
@@ -5047,7 +6327,7 @@
       <c r="L103" s="4"/>
       <c r="M103" s="4"/>
       <c r="N103" s="4" t="str">
-        <f t="shared" ref="N103:N134" si="3">IF(COUNTA(K103:M103)=0,"",SUM(K103:M103))</f>
+        <f t="shared" ref="N103:N106" si="3">IF(COUNTA(K103:M103)=0,"",SUM(K103:M103))</f>
         <v/>
       </c>
       <c r="O103" s="4"/>
@@ -5062,20 +6342,30 @@
       <c r="X103" s="5"/>
       <c r="Y103" s="5"/>
       <c r="Z103" s="5"/>
-    </row>
-    <row r="104" spans="1:26">
+      <c r="AA103" s="13"/>
+      <c r="AB103" s="13"/>
+      <c r="AC103" s="16"/>
+      <c r="AD103" s="16"/>
+      <c r="AE103" s="16"/>
+      <c r="AF103" s="17"/>
+      <c r="AG103" s="16"/>
+      <c r="AH103" s="17"/>
+      <c r="AI103" s="17"/>
+      <c r="AJ103" s="17"/>
+      <c r="AK103" s="14"/>
+      <c r="AL103" s="14"/>
+    </row>
+    <row r="104" spans="1:38">
       <c r="A104" s="2">
         <v>98</v>
       </c>
       <c r="B104" s="3"/>
       <c r="C104" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D104" s="2"/>
       <c r="E104" s="2"/>
-      <c r="F104" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F104" s="2"/>
       <c r="G104" s="2"/>
       <c r="H104" s="2"/>
       <c r="I104" s="2"/>
@@ -5099,20 +6389,30 @@
       <c r="X104" s="5"/>
       <c r="Y104" s="5"/>
       <c r="Z104" s="5"/>
-    </row>
-    <row r="105" spans="1:26">
+      <c r="AA104" s="13"/>
+      <c r="AB104" s="13"/>
+      <c r="AC104" s="16"/>
+      <c r="AD104" s="16"/>
+      <c r="AE104" s="16"/>
+      <c r="AF104" s="17"/>
+      <c r="AG104" s="16"/>
+      <c r="AH104" s="17"/>
+      <c r="AI104" s="17"/>
+      <c r="AJ104" s="17"/>
+      <c r="AK104" s="14"/>
+      <c r="AL104" s="14"/>
+    </row>
+    <row r="105" spans="1:38">
       <c r="A105" s="2">
         <v>99</v>
       </c>
       <c r="B105" s="3"/>
       <c r="C105" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D105" s="2"/>
       <c r="E105" s="2"/>
-      <c r="F105" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F105" s="2"/>
       <c r="G105" s="2"/>
       <c r="H105" s="2"/>
       <c r="I105" s="2"/>
@@ -5136,20 +6436,30 @@
       <c r="X105" s="5"/>
       <c r="Y105" s="5"/>
       <c r="Z105" s="5"/>
-    </row>
-    <row r="106" spans="1:26">
+      <c r="AA105" s="13"/>
+      <c r="AB105" s="13"/>
+      <c r="AC105" s="16"/>
+      <c r="AD105" s="16"/>
+      <c r="AE105" s="16"/>
+      <c r="AF105" s="17"/>
+      <c r="AG105" s="16"/>
+      <c r="AH105" s="17"/>
+      <c r="AI105" s="17"/>
+      <c r="AJ105" s="17"/>
+      <c r="AK105" s="14"/>
+      <c r="AL105" s="14"/>
+    </row>
+    <row r="106" spans="1:38">
       <c r="A106" s="2">
         <v>100</v>
       </c>
       <c r="B106" s="3"/>
       <c r="C106" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D106" s="2"/>
       <c r="E106" s="2"/>
-      <c r="F106" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="F106" s="2"/>
       <c r="G106" s="2"/>
       <c r="H106" s="2"/>
       <c r="I106" s="2"/>
@@ -5173,8 +6483,20 @@
       <c r="X106" s="5"/>
       <c r="Y106" s="5"/>
       <c r="Z106" s="5"/>
-    </row>
-    <row r="107" spans="1:26">
+      <c r="AA106" s="13"/>
+      <c r="AB106" s="13"/>
+      <c r="AC106" s="16"/>
+      <c r="AD106" s="16"/>
+      <c r="AE106" s="16"/>
+      <c r="AF106" s="17"/>
+      <c r="AG106" s="16"/>
+      <c r="AH106" s="17"/>
+      <c r="AI106" s="17"/>
+      <c r="AJ106" s="17"/>
+      <c r="AK106" s="14"/>
+      <c r="AL106" s="14"/>
+    </row>
+    <row r="107" spans="1:38">
       <c r="A107" s="2"/>
       <c r="B107" s="2"/>
       <c r="C107" s="2"/>
@@ -5202,7 +6524,7 @@
       <c r="Y107" s="2"/>
       <c r="Z107" s="2"/>
     </row>
-    <row r="108" spans="1:26">
+    <row r="108" spans="1:38">
       <c r="A108" s="2"/>
       <c r="B108" s="2"/>
       <c r="C108" s="2"/>
@@ -5230,7 +6552,7 @@
       <c r="Y108" s="2"/>
       <c r="Z108" s="2"/>
     </row>
-    <row r="109" spans="1:26">
+    <row r="109" spans="1:38">
       <c r="A109" s="2"/>
       <c r="B109" s="2"/>
       <c r="C109" s="2"/>
@@ -5258,7 +6580,7 @@
       <c r="Y109" s="2"/>
       <c r="Z109" s="2"/>
     </row>
-    <row r="110" spans="1:26">
+    <row r="110" spans="1:38">
       <c r="A110" s="2"/>
       <c r="B110" s="2"/>
       <c r="C110" s="2"/>
@@ -5286,7 +6608,7 @@
       <c r="Y110" s="2"/>
       <c r="Z110" s="2"/>
     </row>
-    <row r="111" spans="1:26">
+    <row r="111" spans="1:38">
       <c r="A111" s="2"/>
       <c r="B111" s="2"/>
       <c r="C111" s="2"/>
@@ -5314,7 +6636,7 @@
       <c r="Y111" s="2"/>
       <c r="Z111" s="2"/>
     </row>
-    <row r="112" spans="1:26">
+    <row r="112" spans="1:38">
       <c r="A112" s="2"/>
       <c r="B112" s="2"/>
       <c r="C112" s="2"/>
@@ -5568,7 +6890,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:Z1"/>
+    <mergeCell ref="A1:AL1"/>
   </mergeCells>
   <phoneticPr fontId="7"/>
   <conditionalFormatting sqref="Q7:T106">
@@ -5587,7 +6909,7 @@
       <formula>Y7="保留"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="8">
+  <dataValidations count="9">
     <dataValidation type="list" sqref="D7:D106" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"T01,T02,T03,T04,T05,T06,T07,T08,T09,T10"</formula1>
     </dataValidation>
@@ -5612,6 +6934,9 @@
     <dataValidation type="list" sqref="Y7:Y106" xr:uid="{00000000-0002-0000-0000-000007000000}">
       <formula1>"合格,不合格,保留"</formula1>
     </dataValidation>
+    <dataValidation type="list" sqref="AK7:AK106" xr:uid="{00000000-0002-0000-0000-000008000000}">
+      <formula1>"未反映,一部反映,反映済,要確認"</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5620,7 +6945,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G20"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -5631,16 +6956,16 @@
     <col min="7" max="7" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="19.5">
-      <c r="A1" s="13" t="s">
-        <v>136</v>
-      </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
+    <row r="1" spans="1:7" ht="19">
+      <c r="A1" s="25" t="s">
+        <v>137</v>
+      </c>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="2"/>
@@ -5651,32 +6976,32 @@
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
     </row>
-    <row r="3" spans="1:7" ht="15">
+    <row r="3" spans="1:7">
       <c r="A3" s="10" t="s">
         <v>12</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E3" s="10" t="s">
         <v>31</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="28.5">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="28">
       <c r="A4" s="5" t="s">
-        <v>142</v>
+        <v>36</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>143</v>
@@ -5697,7 +7022,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="28.5">
+    <row r="5" spans="1:7" ht="28">
       <c r="A5" s="5" t="s">
         <v>149</v>
       </c>
@@ -5720,7 +7045,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="28.5">
+    <row r="6" spans="1:7" ht="28">
       <c r="A6" s="5" t="s">
         <v>155</v>
       </c>
@@ -5743,7 +7068,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="28.5">
+    <row r="7" spans="1:7" ht="28">
       <c r="A7" s="5" t="s">
         <v>161</v>
       </c>
@@ -5766,142 +7091,142 @@
         <v>166</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="28.5">
+    <row r="8" spans="1:7" ht="28">
       <c r="A8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="C8" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="D8" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="E8" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="F8" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="G8" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="G8" s="5" t="s">
+    </row>
+    <row r="9" spans="1:7" ht="28">
+      <c r="A9" s="5" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" ht="28.5">
-      <c r="A9" s="5" t="s">
+      <c r="B9" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="C9" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="D9" s="5" t="s">
         <v>176</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>177</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>146</v>
       </c>
       <c r="F9" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="G9" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="G9" s="5" t="s">
+    </row>
+    <row r="10" spans="1:7" ht="28">
+      <c r="A10" s="5" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" ht="28.5">
-      <c r="A10" s="5" t="s">
+      <c r="B10" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="C10" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="D10" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="E10" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="F10" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="E10" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="F10" s="5" t="s">
+      <c r="G10" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="G10" s="5" t="s">
+    </row>
+    <row r="11" spans="1:7" ht="28">
+      <c r="A11" s="5" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" ht="28.5">
-      <c r="A11" s="5" t="s">
+      <c r="B11" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="C11" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="D11" s="5" t="s">
         <v>188</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>189</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>146</v>
       </c>
       <c r="F11" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="G11" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="G11" s="5" t="s">
+    </row>
+    <row r="12" spans="1:7" ht="28">
+      <c r="A12" s="5" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" ht="28.5">
-      <c r="A12" s="5" t="s">
+      <c r="B12" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="C12" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="D12" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="E12" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="F12" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="G12" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="G12" s="5" t="s">
+    </row>
+    <row r="13" spans="1:7" ht="28">
+      <c r="A13" s="5" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" ht="28.5">
-      <c r="A13" s="5" t="s">
+      <c r="B13" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="C13" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="D13" s="5" t="s">
         <v>201</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>202</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>146</v>
       </c>
       <c r="F13" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="G13" s="5" t="s">
         <v>203</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -5978,22 +7303,22 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:D20"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <dimension ref="A1:D22"/>
+  <sheetFormatPr defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="42" customWidth="1"/>
-    <col min="3" max="3" width="36" customWidth="1"/>
-    <col min="4" max="4" width="30" customWidth="1"/>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="48" customWidth="1"/>
+    <col min="3" max="3" width="30" customWidth="1"/>
+    <col min="4" max="4" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="19.5">
-      <c r="A1" s="13" t="s">
-        <v>205</v>
-      </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
+    <row r="1" spans="1:4" ht="19">
+      <c r="A1" s="25" t="s">
+        <v>204</v>
+      </c>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2"/>
@@ -6001,177 +7326,285 @@
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
     </row>
-    <row r="3" spans="1:4" ht="15">
+    <row r="3" spans="1:4">
       <c r="A3" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="B3" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="C3" s="10" t="s">
         <v>207</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="D3" s="10" t="s">
         <v>208</v>
       </c>
-      <c r="D3" s="10" t="s">
+    </row>
+    <row r="4" spans="1:4" ht="28">
+      <c r="A4" s="5" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" ht="28.5">
-      <c r="A4" s="5" t="s">
+      <c r="B4" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="C4" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="D4" s="5" t="s">
         <v>212</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="C5" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="D5" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="D5" s="5" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="28.5">
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6" s="5" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>218</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="D6" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="28.5">
+    </row>
+    <row r="7" spans="1:4">
       <c r="A7" s="5" t="s">
         <v>7</v>
       </c>
       <c r="B7" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="D7" s="5" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="5" t="s">
         <v>222</v>
       </c>
-      <c r="D7" s="5" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="28.5">
-      <c r="A8" s="5" t="s">
+      <c r="B8" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="C8" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="D8" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="D8" s="5" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="28.5">
+    </row>
+    <row r="9" spans="1:4" ht="28">
       <c r="A9" s="5" t="s">
         <v>16</v>
       </c>
       <c r="B9" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="D9" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="D9" s="5" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
+    </row>
+    <row r="10" spans="1:4" ht="28">
       <c r="A10" s="5" t="s">
         <v>33</v>
       </c>
       <c r="B10" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="D10" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="D10" s="5" t="s">
+    </row>
+    <row r="11" spans="1:4" ht="28" customHeight="1">
+      <c r="A11" s="14" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
+      <c r="B11" s="14" t="s">
+        <v>245</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>246</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="28" customHeight="1">
+      <c r="A12" s="14" t="s">
+        <v>248</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>249</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>250</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="28" customHeight="1">
+      <c r="A13" s="14" t="s">
+        <v>235</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>252</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>253</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="28" customHeight="1">
+      <c r="A14" s="14" t="s">
+        <v>236</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>255</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>256</v>
+      </c>
+      <c r="D14" s="14" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="28" customHeight="1">
+      <c r="A15" s="14" t="s">
+        <v>240</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>258</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>259</v>
+      </c>
+      <c r="D15" s="14" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="28" customHeight="1">
+      <c r="A16" s="14" t="s">
+        <v>241</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>261</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>262</v>
+      </c>
+      <c r="D16" s="14" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="28" customHeight="1">
+      <c r="A17" s="14" t="s">
+        <v>242</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>264</v>
+      </c>
+      <c r="C17" s="14" t="s">
+        <v>265</v>
+      </c>
+      <c r="D17" s="14" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="28" customHeight="1">
+      <c r="A18" s="14" t="s">
+        <v>243</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>267</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>268</v>
+      </c>
+      <c r="D18" s="14" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="28" customHeight="1">
+      <c r="A19" s="14" t="s">
+        <v>270</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>271</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>272</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="28">
+      <c r="A20" s="14" t="s">
+        <v>237</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>274</v>
+      </c>
+      <c r="C20" s="14" t="s">
+        <v>275</v>
+      </c>
+      <c r="D20" s="14" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="28">
+      <c r="A21" s="13" t="s">
+        <v>238</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>277</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>278</v>
+      </c>
+      <c r="D21" s="13" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="28">
+      <c r="A22" s="13" t="s">
+        <v>239</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>280</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>281</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>282</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -6180,4 +7613,510 @@
   <phoneticPr fontId="7"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:F40"/>
+  <sheetFormatPr defaultRowHeight="14"/>
+  <cols>
+    <col min="1" max="6" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="22.65" customHeight="1">
+      <c r="A1" s="26" t="s">
+        <v>283</v>
+      </c>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+    </row>
+    <row r="3" spans="1:6" ht="22.65" customHeight="1">
+      <c r="A3" s="18" t="s">
+        <v>284</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="22.65" customHeight="1">
+      <c r="A4" s="13" t="s">
+        <v>265</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="22.65" customHeight="1">
+      <c r="A5" s="13" t="s">
+        <v>287</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="22.65" customHeight="1">
+      <c r="A6" s="13" t="s">
+        <v>289</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="22.65" customHeight="1">
+      <c r="A7" s="13" t="s">
+        <v>291</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="22.65" customHeight="1">
+      <c r="A8" s="13" t="s">
+        <v>293</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="27" t="s">
+        <v>295</v>
+      </c>
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
+    </row>
+    <row r="11" spans="1:6" ht="14.65" customHeight="1">
+      <c r="A11" s="28" t="s">
+        <v>296</v>
+      </c>
+      <c r="B11" s="28"/>
+      <c r="C11" s="28"/>
+      <c r="D11" s="28"/>
+      <c r="E11" s="28"/>
+      <c r="F11" s="28"/>
+    </row>
+    <row r="12" spans="1:6" ht="14.65" customHeight="1">
+      <c r="A12" s="28"/>
+      <c r="B12" s="28"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="28"/>
+      <c r="F12" s="28"/>
+    </row>
+    <row r="13" spans="1:6" ht="14.65" customHeight="1">
+      <c r="A13" s="28"/>
+      <c r="B13" s="28"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="28"/>
+    </row>
+    <row r="14" spans="1:6" ht="14.65" customHeight="1">
+      <c r="A14" s="28"/>
+      <c r="B14" s="28"/>
+      <c r="C14" s="28"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="28"/>
+    </row>
+    <row r="15" spans="1:6" ht="14.65" customHeight="1">
+      <c r="A15" s="28"/>
+      <c r="B15" s="28"/>
+      <c r="C15" s="28"/>
+      <c r="D15" s="28"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="28"/>
+    </row>
+    <row r="16" spans="1:6" ht="14.65" customHeight="1">
+      <c r="A16" s="28"/>
+      <c r="B16" s="28"/>
+      <c r="C16" s="28"/>
+      <c r="D16" s="28"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="28"/>
+    </row>
+    <row r="17" spans="1:6" ht="14.65" customHeight="1">
+      <c r="A17" s="28"/>
+      <c r="B17" s="28"/>
+      <c r="C17" s="28"/>
+      <c r="D17" s="28"/>
+      <c r="E17" s="28"/>
+      <c r="F17" s="28"/>
+    </row>
+    <row r="18" spans="1:6" ht="14.65" customHeight="1">
+      <c r="A18" s="28"/>
+      <c r="B18" s="28"/>
+      <c r="C18" s="28"/>
+      <c r="D18" s="28"/>
+      <c r="E18" s="28"/>
+      <c r="F18" s="28"/>
+    </row>
+    <row r="19" spans="1:6" ht="14.65" customHeight="1">
+      <c r="A19" s="28"/>
+      <c r="B19" s="28"/>
+      <c r="C19" s="28"/>
+      <c r="D19" s="28"/>
+      <c r="E19" s="28"/>
+      <c r="F19" s="28"/>
+    </row>
+    <row r="20" spans="1:6" ht="14.65" customHeight="1">
+      <c r="A20" s="28"/>
+      <c r="B20" s="28"/>
+      <c r="C20" s="28"/>
+      <c r="D20" s="28"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="28"/>
+    </row>
+    <row r="21" spans="1:6" ht="14.65" customHeight="1">
+      <c r="A21" s="28"/>
+      <c r="B21" s="28"/>
+      <c r="C21" s="28"/>
+      <c r="D21" s="28"/>
+      <c r="E21" s="28"/>
+      <c r="F21" s="28"/>
+    </row>
+    <row r="22" spans="1:6" ht="14.65" customHeight="1">
+      <c r="A22" s="28"/>
+      <c r="B22" s="28"/>
+      <c r="C22" s="28"/>
+      <c r="D22" s="28"/>
+      <c r="E22" s="28"/>
+      <c r="F22" s="28"/>
+    </row>
+    <row r="23" spans="1:6" ht="14.65" customHeight="1">
+      <c r="A23" s="28"/>
+      <c r="B23" s="28"/>
+      <c r="C23" s="28"/>
+      <c r="D23" s="28"/>
+      <c r="E23" s="28"/>
+      <c r="F23" s="28"/>
+    </row>
+    <row r="24" spans="1:6" ht="14.65" customHeight="1">
+      <c r="A24" s="28"/>
+      <c r="B24" s="28"/>
+      <c r="C24" s="28"/>
+      <c r="D24" s="28"/>
+      <c r="E24" s="28"/>
+      <c r="F24" s="28"/>
+    </row>
+    <row r="25" spans="1:6" ht="14.65" customHeight="1">
+      <c r="A25" s="28"/>
+      <c r="B25" s="28"/>
+      <c r="C25" s="28"/>
+      <c r="D25" s="28"/>
+      <c r="E25" s="28"/>
+      <c r="F25" s="28"/>
+    </row>
+    <row r="26" spans="1:6" ht="14.65" customHeight="1">
+      <c r="A26" s="28"/>
+      <c r="B26" s="28"/>
+      <c r="C26" s="28"/>
+      <c r="D26" s="28"/>
+      <c r="E26" s="28"/>
+      <c r="F26" s="28"/>
+    </row>
+    <row r="27" spans="1:6" ht="14.65" customHeight="1">
+      <c r="A27" s="28"/>
+      <c r="B27" s="28"/>
+      <c r="C27" s="28"/>
+      <c r="D27" s="28"/>
+      <c r="E27" s="28"/>
+      <c r="F27" s="28"/>
+    </row>
+    <row r="28" spans="1:6" ht="14.65" customHeight="1">
+      <c r="A28" s="28"/>
+      <c r="B28" s="28"/>
+      <c r="C28" s="28"/>
+      <c r="D28" s="28"/>
+      <c r="E28" s="28"/>
+      <c r="F28" s="28"/>
+    </row>
+    <row r="29" spans="1:6" ht="14.65" customHeight="1">
+      <c r="A29" s="28"/>
+      <c r="B29" s="28"/>
+      <c r="C29" s="28"/>
+      <c r="D29" s="28"/>
+      <c r="E29" s="28"/>
+      <c r="F29" s="28"/>
+    </row>
+    <row r="30" spans="1:6" ht="14.65" customHeight="1">
+      <c r="A30" s="28"/>
+      <c r="B30" s="28"/>
+      <c r="C30" s="28"/>
+      <c r="D30" s="28"/>
+      <c r="E30" s="28"/>
+      <c r="F30" s="28"/>
+    </row>
+    <row r="31" spans="1:6" ht="14.65" customHeight="1">
+      <c r="A31" s="28"/>
+      <c r="B31" s="28"/>
+      <c r="C31" s="28"/>
+      <c r="D31" s="28"/>
+      <c r="E31" s="28"/>
+      <c r="F31" s="28"/>
+    </row>
+    <row r="32" spans="1:6" ht="14.65" customHeight="1">
+      <c r="A32" s="28"/>
+      <c r="B32" s="28"/>
+      <c r="C32" s="28"/>
+      <c r="D32" s="28"/>
+      <c r="E32" s="28"/>
+      <c r="F32" s="28"/>
+    </row>
+    <row r="33" spans="1:6" ht="14.65" customHeight="1">
+      <c r="A33" s="28"/>
+      <c r="B33" s="28"/>
+      <c r="C33" s="28"/>
+      <c r="D33" s="28"/>
+      <c r="E33" s="28"/>
+      <c r="F33" s="28"/>
+    </row>
+    <row r="34" spans="1:6" ht="14.65" customHeight="1">
+      <c r="A34" s="28"/>
+      <c r="B34" s="28"/>
+      <c r="C34" s="28"/>
+      <c r="D34" s="28"/>
+      <c r="E34" s="28"/>
+      <c r="F34" s="28"/>
+    </row>
+    <row r="35" spans="1:6" ht="14.65" customHeight="1">
+      <c r="A35" s="28"/>
+      <c r="B35" s="28"/>
+      <c r="C35" s="28"/>
+      <c r="D35" s="28"/>
+      <c r="E35" s="28"/>
+      <c r="F35" s="28"/>
+    </row>
+    <row r="36" spans="1:6" ht="14.65" customHeight="1">
+      <c r="A36" s="28"/>
+      <c r="B36" s="28"/>
+      <c r="C36" s="28"/>
+      <c r="D36" s="28"/>
+      <c r="E36" s="28"/>
+      <c r="F36" s="28"/>
+    </row>
+    <row r="37" spans="1:6" ht="14.65" customHeight="1">
+      <c r="A37" s="28"/>
+      <c r="B37" s="28"/>
+      <c r="C37" s="28"/>
+      <c r="D37" s="28"/>
+      <c r="E37" s="28"/>
+      <c r="F37" s="28"/>
+    </row>
+    <row r="38" spans="1:6" ht="14.65" customHeight="1">
+      <c r="A38" s="28"/>
+      <c r="B38" s="28"/>
+      <c r="C38" s="28"/>
+      <c r="D38" s="28"/>
+      <c r="E38" s="28"/>
+      <c r="F38" s="28"/>
+    </row>
+    <row r="39" spans="1:6" ht="14.65" customHeight="1">
+      <c r="A39" s="28"/>
+      <c r="B39" s="28"/>
+      <c r="C39" s="28"/>
+      <c r="D39" s="28"/>
+      <c r="E39" s="28"/>
+      <c r="F39" s="28"/>
+    </row>
+    <row r="40" spans="1:6" ht="14.65" customHeight="1">
+      <c r="A40" s="28"/>
+      <c r="B40" s="28"/>
+      <c r="C40" s="28"/>
+      <c r="D40" s="28"/>
+      <c r="E40" s="28"/>
+      <c r="F40" s="28"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A11:F40"/>
+  </mergeCells>
+  <phoneticPr fontId="7"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr defaultRowHeight="14"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="4" width="24" customWidth="1"/>
+    <col min="5" max="5" width="44" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="28">
+      <c r="A1" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="19" t="s">
+        <v>297</v>
+      </c>
+      <c r="C1" s="19" t="s">
+        <v>298</v>
+      </c>
+      <c r="D1" s="19" t="s">
+        <v>299</v>
+      </c>
+      <c r="E1" s="19" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="28">
+      <c r="A2" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="B2" s="13">
+        <v>9</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>300</v>
+      </c>
+      <c r="D2" s="13" t="s">
+        <v>301</v>
+      </c>
+      <c r="E2" s="13" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="13"/>
+      <c r="B3" s="13"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="13"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="13"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="13"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="13"/>
+      <c r="B7" s="13"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="13"/>
+      <c r="B8" s="13"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="13"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="13"/>
+      <c r="B9" s="13"/>
+      <c r="C9" s="13"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="13"/>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="13"/>
+      <c r="B10" s="13"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="13"/>
+      <c r="B11" s="13"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="13"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="13"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="13"/>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="13"/>
+      <c r="B14" s="13"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="13"/>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="13"/>
+      <c r="B15" s="13"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="13"/>
+      <c r="B16" s="13"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="13"/>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="13"/>
+      <c r="B17" s="13"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="13"/>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="13"/>
+      <c r="B18" s="13"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="13"/>
+      <c r="B19" s="13"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13"/>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="13"/>
+      <c r="B20" s="13"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="7"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>